--- a/Data/4DataSet_Graph.xlsx
+++ b/Data/4DataSet_Graph.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\##Paper2\数据整理\OT_QCM2Net\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\niu\Documents\Codex\2026-07-14\7-30-slack-plugin-slack-openai-4\outputs\VLM_DTI_FinalProvenance_20260723\VLM-DTI source code\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2BE9B27-FAD7-41FA-89EA-3DBA8C7BF6E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1121A6F4-96D1-44BC-8CCB-9C1522831B25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="1110" windowWidth="13920" windowHeight="14550" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7515" yWindow="300" windowWidth="16350" windowHeight="12420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="celegans" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="244" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="19">
   <si>
     <t>Dataset</t>
   </si>
@@ -48,9 +48,6 @@
   </si>
   <si>
     <t>Seed</t>
-  </si>
-  <si>
-    <t>BestEpoch</t>
   </si>
   <si>
     <t>AUC_Test</t>
@@ -108,18 +105,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="26">
+  <fonts count="26" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -127,7 +124,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -135,7 +132,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -143,7 +140,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -151,7 +148,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -159,7 +156,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -167,7 +164,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -175,7 +172,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -183,7 +180,7 @@
     <font>
       <sz val="18"/>
       <color theme="3"/>
-      <name val="等线 Light"/>
+      <name val="Yu Gothic Light"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="major"/>
@@ -192,7 +189,7 @@
       <b/>
       <sz val="15"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -201,7 +198,7 @@
       <b/>
       <sz val="13"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -210,7 +207,7 @@
       <b/>
       <sz val="11"/>
       <color theme="3"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -218,7 +215,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -226,7 +223,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -234,7 +231,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C5700"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -242,7 +239,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FF3F3F76"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -251,7 +248,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -260,7 +257,7 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -268,7 +265,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -277,7 +274,7 @@
       <b/>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -285,7 +282,7 @@
     <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -294,7 +291,7 @@
       <i/>
       <sz val="11"/>
       <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -303,7 +300,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -311,14 +308,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="2"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Yu Gothic"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1486,13 +1483,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K31"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="14.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1523,1047 +1520,965 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" s="1" t="s">
+      <c r="B2" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C2" s="1">
         <v>42</v>
       </c>
       <c r="D2" s="4">
-        <v>30</v>
+        <v>0.98009999999999997</v>
       </c>
       <c r="E2" s="4">
-        <v>0.98009999999999997</v>
+        <v>0.98019999999999996</v>
       </c>
       <c r="F2" s="4">
-        <v>0.98019999999999996</v>
+        <v>0.98029999999999995</v>
       </c>
       <c r="G2" s="4">
-        <v>0.98029999999999995</v>
+        <v>0.90859999999999996</v>
       </c>
       <c r="H2" s="4">
-        <v>0.90859999999999996</v>
+        <v>0.95469999999999999</v>
       </c>
       <c r="I2" s="4">
-        <v>0.95469999999999999</v>
+        <v>0.93200000000000005</v>
       </c>
       <c r="J2" s="4">
-        <v>0.93200000000000005</v>
-      </c>
-      <c r="K2" s="4">
         <v>0.93110000000000004</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C3" s="1">
         <v>1234</v>
       </c>
       <c r="D3" s="4">
-        <v>29</v>
+        <v>0.98029999999999995</v>
       </c>
       <c r="E3" s="4">
-        <v>0.98029999999999995</v>
+        <v>0.97960000000000003</v>
       </c>
       <c r="F3" s="4">
         <v>0.97960000000000003</v>
       </c>
       <c r="G3" s="4">
-        <v>0.97960000000000003</v>
+        <v>0.93100000000000005</v>
       </c>
       <c r="H3" s="4">
-        <v>0.93100000000000005</v>
+        <v>0.93600000000000005</v>
       </c>
       <c r="I3" s="4">
-        <v>0.93600000000000005</v>
+        <v>0.93579999999999997</v>
       </c>
       <c r="J3" s="4">
-        <v>0.93579999999999997</v>
-      </c>
-      <c r="K3" s="4">
         <v>0.9335</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
       </c>
       <c r="D4" s="4">
-        <v>28</v>
+        <v>0.9829</v>
       </c>
       <c r="E4" s="4">
-        <v>0.9829</v>
+        <v>0.98329999999999995</v>
       </c>
       <c r="F4" s="4">
         <v>0.98329999999999995</v>
       </c>
       <c r="G4" s="4">
-        <v>0.98329999999999995</v>
+        <v>0.9002</v>
       </c>
       <c r="H4" s="4">
-        <v>0.9002</v>
+        <v>0.9627</v>
       </c>
       <c r="I4" s="4">
-        <v>0.9627</v>
+        <v>0.93069999999999997</v>
       </c>
       <c r="J4" s="4">
-        <v>0.93069999999999997</v>
-      </c>
-      <c r="K4" s="4">
         <v>0.9304</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C5" s="1">
         <v>12345</v>
       </c>
       <c r="D5" s="4">
-        <v>30</v>
+        <v>0.98009999999999997</v>
       </c>
       <c r="E5" s="4">
-        <v>0.98009999999999997</v>
+        <v>0.97970000000000002</v>
       </c>
       <c r="F5" s="4">
         <v>0.97970000000000002</v>
       </c>
       <c r="G5" s="4">
-        <v>0.97970000000000002</v>
+        <v>0.9365</v>
       </c>
       <c r="H5" s="4">
-        <v>0.9365</v>
+        <v>0.94399999999999995</v>
       </c>
       <c r="I5" s="4">
-        <v>0.94399999999999995</v>
+        <v>0.94220000000000004</v>
       </c>
       <c r="J5" s="4">
-        <v>0.94220000000000004</v>
-      </c>
-      <c r="K5" s="4">
         <v>0.94020000000000004</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>11</v>
-      </c>
-      <c r="B6" s="1" t="s">
-        <v>12</v>
       </c>
       <c r="C6" s="1">
         <v>666</v>
       </c>
       <c r="D6" s="4">
-        <v>27</v>
+        <v>0.98570000000000002</v>
       </c>
       <c r="E6" s="4">
-        <v>0.98570000000000002</v>
+        <v>0.98670000000000002</v>
       </c>
       <c r="F6" s="4">
         <v>0.98670000000000002</v>
       </c>
       <c r="G6" s="4">
-        <v>0.98670000000000002</v>
+        <v>0.93679999999999997</v>
       </c>
       <c r="H6" s="4">
-        <v>0.93679999999999997</v>
+        <v>0.94930000000000003</v>
       </c>
       <c r="I6" s="4">
-        <v>0.94930000000000003</v>
+        <v>0.94479999999999997</v>
       </c>
       <c r="J6" s="4">
-        <v>0.94479999999999997</v>
-      </c>
-      <c r="K6" s="4">
         <v>0.94299999999999995</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="D7" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D2:D6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D2:D6),"0.0000")</f>
+        <v>0.9818±0.0025</v>
+      </c>
       <c r="E7" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
-        <v>0.9818±0.0025</v>
+        <f t="shared" ref="E7:J7" si="0" xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
+        <v>0.9819±0.0031</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" ref="F7:K7" si="0" xml:space="preserve"> TEXT(AVERAGE(F2:F6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F2:F6),"0.0000")</f>
+        <f t="shared" si="0"/>
         <v>0.9819±0.0031</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9819±0.0031</v>
+        <v>0.9226±0.0171</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9226±0.0171</v>
+        <v>0.9493±0.0102</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9493±0.0102</v>
+        <v>0.9371±0.0062</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9371±0.0062</v>
-      </c>
-      <c r="K7" t="str">
-        <f t="shared" si="0"/>
         <v>0.9356±0.0056</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>42</v>
       </c>
       <c r="D8" s="4">
-        <v>5</v>
+        <v>0.85660000000000003</v>
       </c>
       <c r="E8" s="4">
-        <v>0.85660000000000003</v>
+        <v>0.80759999999999998</v>
       </c>
       <c r="F8" s="4">
-        <v>0.80759999999999998</v>
+        <v>0.80830000000000002</v>
       </c>
       <c r="G8" s="4">
-        <v>0.80830000000000002</v>
+        <v>0.65610000000000002</v>
       </c>
       <c r="H8" s="4">
-        <v>0.65610000000000002</v>
+        <v>0.86739999999999995</v>
       </c>
       <c r="I8" s="4">
-        <v>0.86739999999999995</v>
+        <v>0.75460000000000005</v>
       </c>
       <c r="J8" s="4">
-        <v>0.75460000000000005</v>
-      </c>
-      <c r="K8" s="4">
         <v>0.747</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>1234</v>
       </c>
       <c r="D9" s="4">
-        <v>4</v>
+        <v>0.86450000000000005</v>
       </c>
       <c r="E9" s="4">
-        <v>0.86450000000000005</v>
+        <v>0.79830000000000001</v>
       </c>
       <c r="F9" s="4">
-        <v>0.79830000000000001</v>
+        <v>0.80420000000000003</v>
       </c>
       <c r="G9" s="4">
-        <v>0.80420000000000003</v>
+        <v>0.70789999999999997</v>
       </c>
       <c r="H9" s="4">
-        <v>0.70789999999999997</v>
+        <v>0.80630000000000002</v>
       </c>
       <c r="I9" s="4">
-        <v>0.80630000000000002</v>
+        <v>0.78010000000000002</v>
       </c>
       <c r="J9" s="4">
-        <v>0.78010000000000002</v>
-      </c>
-      <c r="K9" s="4">
         <v>0.75390000000000001</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1">
         <v>2025</v>
       </c>
       <c r="D10" s="4">
-        <v>27</v>
+        <v>0.88180000000000003</v>
       </c>
       <c r="E10" s="4">
-        <v>0.88180000000000003</v>
+        <v>0.80679999999999996</v>
       </c>
       <c r="F10" s="4">
-        <v>0.80679999999999996</v>
+        <v>0.81410000000000005</v>
       </c>
       <c r="G10" s="4">
-        <v>0.81410000000000005</v>
+        <v>0.74509999999999998</v>
       </c>
       <c r="H10" s="4">
-        <v>0.74509999999999998</v>
+        <v>0.80630000000000002</v>
       </c>
       <c r="I10" s="4">
-        <v>0.80630000000000002</v>
+        <v>0.80389999999999995</v>
       </c>
       <c r="J10" s="4">
-        <v>0.80389999999999995</v>
-      </c>
-      <c r="K10" s="4">
         <v>0.77449999999999997</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>12345</v>
       </c>
       <c r="D11" s="4">
-        <v>20</v>
+        <v>0.89959999999999996</v>
       </c>
       <c r="E11" s="4">
-        <v>0.89959999999999996</v>
+        <v>0.85709999999999997</v>
       </c>
       <c r="F11" s="4">
-        <v>0.85709999999999997</v>
+        <v>0.86180000000000001</v>
       </c>
       <c r="G11" s="4">
-        <v>0.86180000000000001</v>
+        <v>0.75560000000000005</v>
       </c>
       <c r="H11" s="4">
-        <v>0.75560000000000005</v>
+        <v>0.84630000000000005</v>
       </c>
       <c r="I11" s="4">
-        <v>0.84630000000000005</v>
+        <v>0.82150000000000001</v>
       </c>
       <c r="J11" s="4">
-        <v>0.82150000000000001</v>
-      </c>
-      <c r="K11" s="4">
         <v>0.7984</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
         <v>666</v>
       </c>
       <c r="D12" s="4">
-        <v>11</v>
+        <v>0.89190000000000003</v>
       </c>
       <c r="E12" s="4">
-        <v>0.89190000000000003</v>
+        <v>0.84489999999999998</v>
       </c>
       <c r="F12" s="4">
-        <v>0.84489999999999998</v>
+        <v>0.84650000000000003</v>
       </c>
       <c r="G12" s="4">
-        <v>0.84650000000000003</v>
+        <v>0.79500000000000004</v>
       </c>
       <c r="H12" s="4">
-        <v>0.79500000000000004</v>
+        <v>0.80840000000000001</v>
       </c>
       <c r="I12" s="4">
-        <v>0.80840000000000001</v>
+        <v>0.83289999999999997</v>
       </c>
       <c r="J12" s="4">
-        <v>0.83289999999999997</v>
-      </c>
-      <c r="K12" s="4">
         <v>0.80169999999999997</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="D13" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D8:D12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D8:D12),"0.0000")</f>
+        <v>0.8789±0.0181</v>
+      </c>
       <c r="E13" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E8:E12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E8:E12),"0.0000")</f>
-        <v>0.8789±0.0181</v>
+        <f t="shared" ref="E13:J13" si="1" xml:space="preserve"> TEXT(AVERAGE(E8:E12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E8:E12),"0.0000")</f>
+        <v>0.8229±0.0262</v>
       </c>
       <c r="F13" t="str">
-        <f t="shared" ref="F13:K13" si="1" xml:space="preserve"> TEXT(AVERAGE(F8:F12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F8:F12),"0.0000")</f>
-        <v>0.8229±0.0262</v>
+        <f t="shared" si="1"/>
+        <v>0.8270±0.0256</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8270±0.0256</v>
+        <v>0.7319±0.0525</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="1"/>
-        <v>0.7319±0.0525</v>
+        <v>0.8269±0.0283</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8269±0.0283</v>
+        <v>0.7986±0.0317</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
-        <v>0.7986±0.0317</v>
-      </c>
-      <c r="K13" t="str">
-        <f t="shared" si="1"/>
         <v>0.7751±0.0249</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1">
         <v>42</v>
       </c>
       <c r="D14" s="4">
-        <v>28</v>
+        <v>0.96409999999999996</v>
       </c>
       <c r="E14" s="4">
-        <v>0.96409999999999996</v>
+        <v>0.97440000000000004</v>
       </c>
       <c r="F14" s="4">
         <v>0.97440000000000004</v>
       </c>
       <c r="G14" s="4">
-        <v>0.97440000000000004</v>
+        <v>0.9637</v>
       </c>
       <c r="H14" s="4">
-        <v>0.9637</v>
+        <v>0.86250000000000004</v>
       </c>
       <c r="I14" s="4">
-        <v>0.86250000000000004</v>
+        <v>0.90290000000000004</v>
       </c>
       <c r="J14" s="4">
-        <v>0.90290000000000004</v>
-      </c>
-      <c r="K14" s="4">
         <v>0.91020000000000001</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1">
         <v>1234</v>
       </c>
       <c r="D15" s="4">
-        <v>27</v>
+        <v>0.95289999999999997</v>
       </c>
       <c r="E15" s="4">
-        <v>0.95289999999999997</v>
+        <v>0.96760000000000002</v>
       </c>
       <c r="F15" s="4">
         <v>0.96760000000000002</v>
       </c>
       <c r="G15" s="4">
-        <v>0.96760000000000002</v>
+        <v>0.94989999999999997</v>
       </c>
       <c r="H15" s="4">
-        <v>0.94989999999999997</v>
+        <v>0.79369999999999996</v>
       </c>
       <c r="I15" s="4">
-        <v>0.79369999999999996</v>
+        <v>0.85840000000000005</v>
       </c>
       <c r="J15" s="4">
-        <v>0.85840000000000005</v>
-      </c>
-      <c r="K15" s="4">
         <v>0.86480000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1">
         <v>2025</v>
       </c>
       <c r="D16" s="4">
-        <v>29</v>
+        <v>0.96499999999999997</v>
       </c>
       <c r="E16" s="4">
-        <v>0.96499999999999997</v>
+        <v>0.97360000000000002</v>
       </c>
       <c r="F16" s="4">
         <v>0.97360000000000002</v>
       </c>
       <c r="G16" s="4">
-        <v>0.97360000000000002</v>
+        <v>0.95240000000000002</v>
       </c>
       <c r="H16" s="4">
-        <v>0.95240000000000002</v>
+        <v>0.87360000000000004</v>
       </c>
       <c r="I16" s="4">
-        <v>0.87360000000000004</v>
+        <v>0.90290000000000004</v>
       </c>
       <c r="J16" s="4">
-        <v>0.90290000000000004</v>
-      </c>
-      <c r="K16" s="4">
         <v>0.9113</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1">
         <v>12345</v>
       </c>
       <c r="D17" s="4">
-        <v>25</v>
+        <v>0.96540000000000004</v>
       </c>
       <c r="E17" s="4">
-        <v>0.96540000000000004</v>
+        <v>0.97440000000000004</v>
       </c>
       <c r="F17" s="4">
         <v>0.97440000000000004</v>
       </c>
       <c r="G17" s="4">
-        <v>0.97440000000000004</v>
+        <v>0.97219999999999995</v>
       </c>
       <c r="H17" s="4">
-        <v>0.97219999999999995</v>
+        <v>0.84570000000000001</v>
       </c>
       <c r="I17" s="4">
-        <v>0.84570000000000001</v>
+        <v>0.89810000000000001</v>
       </c>
       <c r="J17" s="4">
-        <v>0.89810000000000001</v>
-      </c>
-      <c r="K17" s="4">
         <v>0.90459999999999996</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1">
         <v>666</v>
       </c>
       <c r="D18" s="4">
-        <v>27</v>
+        <v>0.96399999999999997</v>
       </c>
       <c r="E18" s="4">
-        <v>0.96399999999999997</v>
+        <v>0.97419999999999995</v>
       </c>
       <c r="F18" s="4">
         <v>0.97419999999999995</v>
       </c>
       <c r="G18" s="4">
-        <v>0.97419999999999995</v>
+        <v>0.94920000000000004</v>
       </c>
       <c r="H18" s="4">
-        <v>0.94920000000000004</v>
+        <v>0.86799999999999999</v>
       </c>
       <c r="I18" s="4">
-        <v>0.86799999999999999</v>
+        <v>0.89810000000000001</v>
       </c>
       <c r="J18" s="4">
-        <v>0.89810000000000001</v>
-      </c>
-      <c r="K18" s="4">
         <v>0.90680000000000005</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="D19" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D14:D18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D14:D18),"0.0000")</f>
+        <v>0.9623±0.0053</v>
+      </c>
       <c r="E19" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
-        <v>0.9623±0.0053</v>
+        <f t="shared" ref="E19:J19" si="2" xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
+        <v>0.9728±0.0029</v>
       </c>
       <c r="F19" t="str">
-        <f t="shared" ref="F19:K19" si="2" xml:space="preserve"> TEXT(AVERAGE(F14:F18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F14:F18),"0.0000")</f>
+        <f t="shared" si="2"/>
         <v>0.9728±0.0029</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="2"/>
-        <v>0.9728±0.0029</v>
+        <v>0.9575±0.0101</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" si="2"/>
-        <v>0.9575±0.0101</v>
+        <v>0.8487±0.0325</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" si="2"/>
-        <v>0.8487±0.0325</v>
+        <v>0.8921±0.0190</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="2"/>
-        <v>0.8921±0.0190</v>
-      </c>
-      <c r="K19" t="str">
-        <f t="shared" si="2"/>
         <v>0.8995±0.0196</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1">
         <v>42</v>
       </c>
       <c r="D20" s="4">
-        <v>27</v>
+        <v>0.97619999999999996</v>
       </c>
       <c r="E20" s="4">
-        <v>0.97619999999999996</v>
+        <v>0.97919999999999996</v>
       </c>
       <c r="F20" s="4">
-        <v>0.97919999999999996</v>
+        <v>0.97929999999999995</v>
       </c>
       <c r="G20" s="4">
-        <v>0.97929999999999995</v>
+        <v>0.90069999999999995</v>
       </c>
       <c r="H20" s="4">
-        <v>0.90069999999999995</v>
+        <v>0.91279999999999994</v>
       </c>
       <c r="I20" s="4">
-        <v>0.91279999999999994</v>
+        <v>0.90410000000000001</v>
       </c>
       <c r="J20" s="4">
-        <v>0.90410000000000001</v>
-      </c>
-      <c r="K20" s="4">
         <v>0.90669999999999995</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1">
         <v>1234</v>
       </c>
       <c r="D21" s="4">
-        <v>29</v>
+        <v>0.98480000000000001</v>
       </c>
       <c r="E21" s="4">
-        <v>0.98480000000000001</v>
+        <v>0.98660000000000003</v>
       </c>
       <c r="F21" s="4">
         <v>0.98660000000000003</v>
       </c>
       <c r="G21" s="4">
-        <v>0.98660000000000003</v>
+        <v>0.89380000000000004</v>
       </c>
       <c r="H21" s="4">
-        <v>0.89380000000000004</v>
+        <v>0.9597</v>
       </c>
       <c r="I21" s="4">
-        <v>0.9597</v>
+        <v>0.92120000000000002</v>
       </c>
       <c r="J21" s="4">
-        <v>0.92120000000000002</v>
-      </c>
-      <c r="K21" s="4">
         <v>0.92559999999999998</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="1">
         <v>2025</v>
       </c>
       <c r="D22" s="4">
-        <v>30</v>
+        <v>0.98299999999999998</v>
       </c>
       <c r="E22" s="4">
-        <v>0.98299999999999998</v>
+        <v>0.98540000000000005</v>
       </c>
       <c r="F22" s="4">
-        <v>0.98540000000000005</v>
+        <v>0.98550000000000004</v>
       </c>
       <c r="G22" s="4">
-        <v>0.98550000000000004</v>
+        <v>0.93379999999999996</v>
       </c>
       <c r="H22" s="4">
-        <v>0.93379999999999996</v>
+        <v>0.94630000000000003</v>
       </c>
       <c r="I22" s="4">
-        <v>0.94630000000000003</v>
+        <v>0.93840000000000001</v>
       </c>
       <c r="J22" s="4">
-        <v>0.93840000000000001</v>
-      </c>
-      <c r="K22" s="4">
         <v>0.94</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1">
         <v>12345</v>
       </c>
       <c r="D23" s="4">
-        <v>28</v>
+        <v>0.98429999999999995</v>
       </c>
       <c r="E23" s="4">
-        <v>0.98429999999999995</v>
+        <v>0.98709999999999998</v>
       </c>
       <c r="F23" s="4">
-        <v>0.98709999999999998</v>
+        <v>0.98719999999999997</v>
       </c>
       <c r="G23" s="4">
-        <v>0.98719999999999997</v>
+        <v>0.90910000000000002</v>
       </c>
       <c r="H23" s="4">
-        <v>0.90910000000000002</v>
+        <v>0.93959999999999999</v>
       </c>
       <c r="I23" s="4">
-        <v>0.93959999999999999</v>
+        <v>0.92120000000000002</v>
       </c>
       <c r="J23" s="4">
-        <v>0.92120000000000002</v>
-      </c>
-      <c r="K23" s="4">
         <v>0.92410000000000003</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1">
         <v>666</v>
       </c>
       <c r="D24" s="4">
-        <v>29</v>
+        <v>0.98750000000000004</v>
       </c>
       <c r="E24" s="4">
-        <v>0.98750000000000004</v>
+        <v>0.98899999999999999</v>
       </c>
       <c r="F24" s="4">
         <v>0.98899999999999999</v>
       </c>
       <c r="G24" s="4">
-        <v>0.98899999999999999</v>
+        <v>0.95950000000000002</v>
       </c>
       <c r="H24" s="4">
-        <v>0.95950000000000002</v>
+        <v>0.95299999999999996</v>
       </c>
       <c r="I24" s="4">
-        <v>0.95299999999999996</v>
+        <v>0.95550000000000002</v>
       </c>
       <c r="J24" s="4">
-        <v>0.95550000000000002</v>
-      </c>
-      <c r="K24" s="4">
         <v>0.95620000000000005</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="D25" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D20:D24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D20:D24),"0.0000")</f>
+        <v>0.9832±0.0042</v>
+      </c>
       <c r="E25" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
-        <v>0.9832±0.0042</v>
+        <f t="shared" ref="E25:J25" si="3" xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
+        <v>0.9855±0.0037</v>
       </c>
       <c r="F25" t="str">
-        <f t="shared" ref="F25:K25" si="3" xml:space="preserve"> TEXT(AVERAGE(F20:F24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F20:F24),"0.0000")</f>
+        <f t="shared" si="3"/>
         <v>0.9855±0.0037</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9855±0.0037</v>
+        <v>0.9194±0.0270</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9194±0.0270</v>
+        <v>0.9423±0.0181</v>
       </c>
       <c r="I25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9423±0.0181</v>
+        <v>0.9281±0.0195</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9281±0.0195</v>
-      </c>
-      <c r="K25" t="str">
-        <f t="shared" si="3"/>
         <v>0.9305±0.0186</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>42</v>
       </c>
       <c r="D26" s="4">
-        <v>27</v>
+        <v>0.98939999999999995</v>
       </c>
       <c r="E26" s="4">
-        <v>0.98939999999999995</v>
+        <v>0.99170000000000003</v>
       </c>
       <c r="F26" s="4">
-        <v>0.99170000000000003</v>
+        <v>0.99180000000000001</v>
       </c>
       <c r="G26" s="4">
-        <v>0.99180000000000001</v>
+        <v>0.9577</v>
       </c>
       <c r="H26" s="4">
-        <v>0.9577</v>
+        <v>0.97840000000000005</v>
       </c>
       <c r="I26" s="4">
-        <v>0.97840000000000005</v>
+        <v>0.96399999999999997</v>
       </c>
       <c r="J26" s="4">
-        <v>0.96399999999999997</v>
-      </c>
-      <c r="K26" s="4">
         <v>0.96799999999999997</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C27" s="1">
         <v>1234</v>
       </c>
       <c r="D27" s="4">
-        <v>29</v>
+        <v>0.98560000000000003</v>
       </c>
       <c r="E27" s="4">
-        <v>0.98560000000000003</v>
+        <v>0.98850000000000005</v>
       </c>
       <c r="F27" s="4">
         <v>0.98850000000000005</v>
       </c>
       <c r="G27" s="4">
-        <v>0.98850000000000005</v>
+        <v>0.93659999999999999</v>
       </c>
       <c r="H27" s="4">
-        <v>0.93659999999999999</v>
+        <v>0.95679999999999998</v>
       </c>
       <c r="I27" s="4">
-        <v>0.95679999999999998</v>
+        <v>0.94</v>
       </c>
       <c r="J27" s="4">
-        <v>0.94</v>
-      </c>
-      <c r="K27" s="4">
         <v>0.9466</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1">
         <v>2025</v>
       </c>
       <c r="D28" s="4">
-        <v>26</v>
+        <v>0.99</v>
       </c>
       <c r="E28" s="4">
-        <v>0.99</v>
+        <v>0.99239999999999995</v>
       </c>
       <c r="F28" s="4">
         <v>0.99239999999999995</v>
       </c>
       <c r="G28" s="4">
-        <v>0.99239999999999995</v>
+        <v>0.9577</v>
       </c>
       <c r="H28" s="4">
-        <v>0.9577</v>
+        <v>0.97840000000000005</v>
       </c>
       <c r="I28" s="4">
-        <v>0.97840000000000005</v>
+        <v>0.96399999999999997</v>
       </c>
       <c r="J28" s="4">
-        <v>0.96399999999999997</v>
-      </c>
-      <c r="K28" s="4">
         <v>0.96799999999999997</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" s="1">
         <v>12345</v>
       </c>
       <c r="D29" s="4">
-        <v>30</v>
+        <v>0.98860000000000003</v>
       </c>
       <c r="E29" s="4">
-        <v>0.98860000000000003</v>
+        <v>0.9909</v>
       </c>
       <c r="F29" s="4">
-        <v>0.9909</v>
+        <v>0.99099999999999999</v>
       </c>
       <c r="G29" s="4">
-        <v>0.99099999999999999</v>
+        <v>0.94369999999999998</v>
       </c>
       <c r="H29" s="4">
-        <v>0.94369999999999998</v>
+        <v>0.96399999999999997</v>
       </c>
       <c r="I29" s="4">
-        <v>0.96399999999999997</v>
+        <v>0.94799999999999995</v>
       </c>
       <c r="J29" s="4">
-        <v>0.94799999999999995</v>
-      </c>
-      <c r="K29" s="4">
         <v>0.95369999999999999</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" s="1">
         <v>666</v>
       </c>
       <c r="D30" s="4">
-        <v>25</v>
+        <v>0.98919999999999997</v>
       </c>
       <c r="E30" s="4">
-        <v>0.98919999999999997</v>
+        <v>0.99270000000000003</v>
       </c>
       <c r="F30" s="4">
         <v>0.99270000000000003</v>
       </c>
       <c r="G30" s="4">
-        <v>0.99270000000000003</v>
+        <v>0.94410000000000005</v>
       </c>
       <c r="H30" s="4">
-        <v>0.94410000000000005</v>
+        <v>0.97119999999999995</v>
       </c>
       <c r="I30" s="4">
-        <v>0.97119999999999995</v>
+        <v>0.95199999999999996</v>
       </c>
       <c r="J30" s="4">
-        <v>0.95199999999999996</v>
-      </c>
-      <c r="K30" s="4">
         <v>0.95740000000000003</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D31" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D26:D30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D26:D30),"0.0000")</f>
+        <v>0.9886±0.0017</v>
+      </c>
       <c r="E31" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
-        <v>0.9886±0.0017</v>
+        <f t="shared" ref="E31:J31" si="4" xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
+        <v>0.9912±0.0017</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" ref="F31:K31" si="4" xml:space="preserve"> TEXT(AVERAGE(F26:F30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F26:F30),"0.0000")</f>
-        <v>0.9912±0.0017</v>
+        <f t="shared" si="4"/>
+        <v>0.9913±0.0017</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9913±0.0017</v>
+        <v>0.9480±0.0094</v>
       </c>
       <c r="H31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9480±0.0094</v>
+        <v>0.9698±0.0094</v>
       </c>
       <c r="I31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9698±0.0094</v>
+        <v>0.9536±0.0104</v>
       </c>
       <c r="J31" t="str">
-        <f t="shared" si="4"/>
-        <v>0.9536±0.0104</v>
-      </c>
-      <c r="K31" t="str">
         <f t="shared" si="4"/>
         <v>0.9587±0.0093</v>
       </c>
@@ -2577,10 +2492,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D4FE8A1-466E-4044-9083-70D3ABB3121B}">
-  <dimension ref="A1:K31"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2611,1047 +2526,965 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1">
         <v>42</v>
       </c>
       <c r="D2" s="4">
-        <v>30</v>
+        <v>0.97150000000000003</v>
       </c>
       <c r="E2" s="4">
-        <v>0.97150000000000003</v>
+        <v>0.97840000000000005</v>
       </c>
       <c r="F2" s="4">
-        <v>0.97840000000000005</v>
+        <v>0.97850000000000004</v>
       </c>
       <c r="G2" s="4">
-        <v>0.97850000000000004</v>
+        <v>0.89319999999999999</v>
       </c>
       <c r="H2" s="4">
-        <v>0.89319999999999999</v>
+        <v>0.93679999999999997</v>
       </c>
       <c r="I2" s="4">
-        <v>0.93679999999999997</v>
+        <v>0.90939999999999999</v>
       </c>
       <c r="J2" s="4">
-        <v>0.90939999999999999</v>
-      </c>
-      <c r="K2" s="4">
         <v>0.91439999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>1234</v>
       </c>
       <c r="D3" s="4">
-        <v>28</v>
+        <v>0.97050000000000003</v>
       </c>
       <c r="E3" s="4">
-        <v>0.97050000000000003</v>
+        <v>0.97599999999999998</v>
       </c>
       <c r="F3" s="4">
-        <v>0.97599999999999998</v>
+        <v>0.97609999999999997</v>
       </c>
       <c r="G3" s="4">
-        <v>0.97609999999999997</v>
+        <v>0.90280000000000005</v>
       </c>
       <c r="H3" s="4">
-        <v>0.90280000000000005</v>
+        <v>0.93389999999999995</v>
       </c>
       <c r="I3" s="4">
-        <v>0.93389999999999995</v>
+        <v>0.91379999999999995</v>
       </c>
       <c r="J3" s="4">
-        <v>0.91379999999999995</v>
-      </c>
-      <c r="K3" s="4">
         <v>0.91810000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
       </c>
       <c r="D4" s="4">
-        <v>30</v>
+        <v>0.97060000000000002</v>
       </c>
       <c r="E4" s="4">
-        <v>0.97060000000000002</v>
+        <v>0.97699999999999998</v>
       </c>
       <c r="F4" s="4">
         <v>0.97699999999999998</v>
       </c>
       <c r="G4" s="4">
-        <v>0.97699999999999998</v>
+        <v>0.94750000000000001</v>
       </c>
       <c r="H4" s="4">
-        <v>0.94750000000000001</v>
+        <v>0.88219999999999998</v>
       </c>
       <c r="I4" s="4">
-        <v>0.88219999999999998</v>
+        <v>0.91379999999999995</v>
       </c>
       <c r="J4" s="4">
-        <v>0.91379999999999995</v>
-      </c>
-      <c r="K4" s="4">
         <v>0.91369999999999996</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1">
         <v>12345</v>
       </c>
       <c r="D5" s="4">
-        <v>30</v>
+        <v>0.97260000000000002</v>
       </c>
       <c r="E5" s="4">
-        <v>0.97260000000000002</v>
+        <v>0.9788</v>
       </c>
       <c r="F5" s="4">
-        <v>0.9788</v>
+        <v>0.97889999999999999</v>
       </c>
       <c r="G5" s="4">
-        <v>0.97889999999999999</v>
+        <v>0.95989999999999998</v>
       </c>
       <c r="H5" s="4">
-        <v>0.95989999999999998</v>
+        <v>0.89370000000000005</v>
       </c>
       <c r="I5" s="4">
-        <v>0.89370000000000005</v>
+        <v>0.92569999999999997</v>
       </c>
       <c r="J5" s="4">
-        <v>0.92569999999999997</v>
-      </c>
-      <c r="K5" s="4">
         <v>0.92559999999999998</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1">
         <v>666</v>
       </c>
       <c r="D6" s="4">
-        <v>29</v>
+        <v>0.97170000000000001</v>
       </c>
       <c r="E6" s="4">
-        <v>0.97170000000000001</v>
+        <v>0.97809999999999997</v>
       </c>
       <c r="F6" s="4">
         <v>0.97809999999999997</v>
       </c>
       <c r="G6" s="4">
-        <v>0.97809999999999997</v>
+        <v>0.96150000000000002</v>
       </c>
       <c r="H6" s="4">
-        <v>0.96150000000000002</v>
+        <v>0.86209999999999998</v>
       </c>
       <c r="I6" s="4">
-        <v>0.86209999999999998</v>
+        <v>0.91080000000000005</v>
       </c>
       <c r="J6" s="4">
-        <v>0.91080000000000005</v>
-      </c>
-      <c r="K6" s="4">
         <v>0.90910000000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="D7" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D2:D6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D2:D6),"0.0000")</f>
+        <v>0.9714±0.0009</v>
+      </c>
       <c r="E7" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
-        <v>0.9714±0.0009</v>
+        <f t="shared" ref="E7:J7" si="0" xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
+        <v>0.9777±0.0011</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" ref="F7:K7" si="0" xml:space="preserve"> TEXT(AVERAGE(F2:F6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F2:F6),"0.0000")</f>
+        <f t="shared" si="0"/>
         <v>0.9777±0.0011</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9777±0.0011</v>
+        <v>0.9330±0.0326</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9330±0.0326</v>
+        <v>0.9017±0.0327</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9017±0.0327</v>
+        <v>0.9147±0.0064</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9147±0.0064</v>
-      </c>
-      <c r="K7" t="str">
-        <f t="shared" si="0"/>
         <v>0.9162±0.0062</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>42</v>
       </c>
       <c r="D8" s="4">
-        <v>27</v>
+        <v>0.94310000000000005</v>
       </c>
       <c r="E8" s="4">
-        <v>0.94310000000000005</v>
+        <v>0.92600000000000005</v>
       </c>
       <c r="F8" s="4">
-        <v>0.92600000000000005</v>
+        <v>0.92620000000000002</v>
       </c>
       <c r="G8" s="4">
-        <v>0.92620000000000002</v>
+        <v>0.82069999999999999</v>
       </c>
       <c r="H8" s="4">
-        <v>0.82069999999999999</v>
+        <v>0.86180000000000001</v>
       </c>
       <c r="I8" s="4">
-        <v>0.86180000000000001</v>
+        <v>0.8579</v>
       </c>
       <c r="J8" s="4">
-        <v>0.8579</v>
-      </c>
-      <c r="K8" s="4">
         <v>0.84079999999999999</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>1234</v>
       </c>
       <c r="D9" s="4">
-        <v>8</v>
+        <v>0.90259999999999996</v>
       </c>
       <c r="E9" s="4">
-        <v>0.90259999999999996</v>
+        <v>0.87729999999999997</v>
       </c>
       <c r="F9" s="4">
-        <v>0.87729999999999997</v>
+        <v>0.87780000000000002</v>
       </c>
       <c r="G9" s="4">
-        <v>0.87780000000000002</v>
+        <v>0.76319999999999999</v>
       </c>
       <c r="H9" s="4">
-        <v>0.76319999999999999</v>
+        <v>0.84630000000000005</v>
       </c>
       <c r="I9" s="4">
-        <v>0.84630000000000005</v>
+        <v>0.81879999999999997</v>
       </c>
       <c r="J9" s="4">
-        <v>0.81879999999999997</v>
-      </c>
-      <c r="K9" s="4">
         <v>0.80259999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1">
         <v>2025</v>
       </c>
       <c r="D10" s="4">
-        <v>18</v>
+        <v>0.93169999999999997</v>
       </c>
       <c r="E10" s="4">
-        <v>0.93169999999999997</v>
+        <v>0.9133</v>
       </c>
       <c r="F10" s="4">
-        <v>0.9133</v>
+        <v>0.91369999999999996</v>
       </c>
       <c r="G10" s="4">
-        <v>0.91369999999999996</v>
+        <v>0.8</v>
       </c>
       <c r="H10" s="4">
-        <v>0.8</v>
+        <v>0.84970000000000001</v>
       </c>
       <c r="I10" s="4">
-        <v>0.84970000000000001</v>
+        <v>0.84209999999999996</v>
       </c>
       <c r="J10" s="4">
-        <v>0.84209999999999996</v>
-      </c>
-      <c r="K10" s="4">
         <v>0.82410000000000005</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>12345</v>
       </c>
       <c r="D11" s="4">
-        <v>30</v>
+        <v>0.95209999999999995</v>
       </c>
       <c r="E11" s="4">
-        <v>0.95209999999999995</v>
+        <v>0.93010000000000004</v>
       </c>
       <c r="F11" s="4">
-        <v>0.93010000000000004</v>
+        <v>0.93059999999999998</v>
       </c>
       <c r="G11" s="4">
-        <v>0.93059999999999998</v>
+        <v>0.87929999999999997</v>
       </c>
       <c r="H11" s="4">
-        <v>0.87929999999999997</v>
+        <v>0.83069999999999999</v>
       </c>
       <c r="I11" s="4">
-        <v>0.83069999999999999</v>
+        <v>0.87670000000000003</v>
       </c>
       <c r="J11" s="4">
-        <v>0.87670000000000003</v>
-      </c>
-      <c r="K11" s="4">
         <v>0.85429999999999995</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
         <v>666</v>
       </c>
       <c r="D12" s="4">
-        <v>30</v>
+        <v>0.93859999999999999</v>
       </c>
       <c r="E12" s="4">
-        <v>0.93859999999999999</v>
+        <v>0.92249999999999999</v>
       </c>
       <c r="F12" s="4">
-        <v>0.92249999999999999</v>
+        <v>0.92259999999999998</v>
       </c>
       <c r="G12" s="4">
-        <v>0.92259999999999998</v>
+        <v>0.86199999999999999</v>
       </c>
       <c r="H12" s="4">
-        <v>0.86199999999999999</v>
+        <v>0.78759999999999997</v>
       </c>
       <c r="I12" s="4">
-        <v>0.78759999999999997</v>
+        <v>0.85260000000000002</v>
       </c>
       <c r="J12" s="4">
-        <v>0.85260000000000002</v>
-      </c>
-      <c r="K12" s="4">
         <v>0.82310000000000005</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="D13" t="str">
+        <f t="shared" ref="D13:J13" si="1" xml:space="preserve"> TEXT(AVERAGE(D8:D12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D8:D12),"0.0000")</f>
+        <v>0.9336±0.0189</v>
+      </c>
       <c r="E13" t="str">
-        <f t="shared" ref="E13:K13" si="1" xml:space="preserve"> TEXT(AVERAGE(E8:E12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E8:E12),"0.0000")</f>
-        <v>0.9336±0.0189</v>
+        <f t="shared" si="1"/>
+        <v>0.9138±0.0213</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="1"/>
-        <v>0.9138±0.0213</v>
+        <v>0.9142±0.0213</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="1"/>
-        <v>0.9142±0.0213</v>
+        <v>0.8250±0.0469</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8250±0.0469</v>
+        <v>0.8352±0.0288</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8352±0.0288</v>
+        <v>0.8496±0.0213</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8496±0.0213</v>
-      </c>
-      <c r="K13" t="str">
-        <f t="shared" si="1"/>
         <v>0.8290±0.0196</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1">
         <v>42</v>
       </c>
       <c r="D14" s="4">
-        <v>30</v>
+        <v>0.95820000000000005</v>
       </c>
       <c r="E14" s="4">
-        <v>0.95820000000000005</v>
+        <v>0.94299999999999995</v>
       </c>
       <c r="F14" s="4">
-        <v>0.94299999999999995</v>
+        <v>0.94310000000000005</v>
       </c>
       <c r="G14" s="4">
-        <v>0.94310000000000005</v>
+        <v>0.8498</v>
       </c>
       <c r="H14" s="4">
-        <v>0.8498</v>
+        <v>0.85709999999999997</v>
       </c>
       <c r="I14" s="4">
-        <v>0.85709999999999997</v>
+        <v>0.88200000000000001</v>
       </c>
       <c r="J14" s="4">
-        <v>0.88200000000000001</v>
-      </c>
-      <c r="K14" s="4">
         <v>0.85340000000000005</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1">
         <v>1234</v>
       </c>
       <c r="D15" s="4">
-        <v>30</v>
+        <v>0.96289999999999998</v>
       </c>
       <c r="E15" s="4">
-        <v>0.96289999999999998</v>
+        <v>0.94789999999999996</v>
       </c>
       <c r="F15" s="4">
-        <v>0.94789999999999996</v>
+        <v>0.94799999999999995</v>
       </c>
       <c r="G15" s="4">
-        <v>0.94799999999999995</v>
+        <v>0.86750000000000005</v>
       </c>
       <c r="H15" s="4">
-        <v>0.86750000000000005</v>
+        <v>0.87880000000000003</v>
       </c>
       <c r="I15" s="4">
-        <v>0.87880000000000003</v>
+        <v>0.89770000000000005</v>
       </c>
       <c r="J15" s="4">
-        <v>0.89770000000000005</v>
-      </c>
-      <c r="K15" s="4">
         <v>0.87309999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1">
         <v>2025</v>
       </c>
       <c r="D16" s="4">
-        <v>27</v>
+        <v>0.96099999999999997</v>
       </c>
       <c r="E16" s="4">
-        <v>0.96099999999999997</v>
+        <v>0.94630000000000003</v>
       </c>
       <c r="F16" s="4">
         <v>0.94630000000000003</v>
       </c>
       <c r="G16" s="4">
-        <v>0.94630000000000003</v>
+        <v>0.86180000000000001</v>
       </c>
       <c r="H16" s="4">
-        <v>0.86180000000000001</v>
+        <v>0.86360000000000003</v>
       </c>
       <c r="I16" s="4">
-        <v>0.86360000000000003</v>
+        <v>0.88990000000000002</v>
       </c>
       <c r="J16" s="4">
-        <v>0.88990000000000002</v>
-      </c>
-      <c r="K16" s="4">
         <v>0.86270000000000002</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1">
         <v>12345</v>
       </c>
       <c r="D17" s="4">
-        <v>30</v>
+        <v>0.95420000000000005</v>
       </c>
       <c r="E17" s="4">
-        <v>0.95420000000000005</v>
+        <v>0.93679999999999997</v>
       </c>
       <c r="F17" s="4">
-        <v>0.93679999999999997</v>
+        <v>0.93689999999999996</v>
       </c>
       <c r="G17" s="4">
-        <v>0.93689999999999996</v>
+        <v>0.89080000000000004</v>
       </c>
       <c r="H17" s="4">
-        <v>0.89080000000000004</v>
+        <v>0.77710000000000001</v>
       </c>
       <c r="I17" s="4">
-        <v>0.77710000000000001</v>
+        <v>0.87250000000000005</v>
       </c>
       <c r="J17" s="4">
-        <v>0.87250000000000005</v>
-      </c>
-      <c r="K17" s="4">
         <v>0.83009999999999995</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1">
         <v>666</v>
       </c>
       <c r="D18" s="4">
-        <v>30</v>
+        <v>0.96009999999999995</v>
       </c>
       <c r="E18" s="4">
-        <v>0.96009999999999995</v>
+        <v>0.94410000000000005</v>
       </c>
       <c r="F18" s="4">
         <v>0.94410000000000005</v>
       </c>
       <c r="G18" s="4">
-        <v>0.94410000000000005</v>
+        <v>0.88380000000000003</v>
       </c>
       <c r="H18" s="4">
-        <v>0.88380000000000003</v>
+        <v>0.83979999999999999</v>
       </c>
       <c r="I18" s="4">
-        <v>0.83979999999999999</v>
+        <v>0.89159999999999995</v>
       </c>
       <c r="J18" s="4">
-        <v>0.89159999999999995</v>
-      </c>
-      <c r="K18" s="4">
         <v>0.86129999999999995</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="D19" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D14:D18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D14:D18),"0.0000")</f>
+        <v>0.9593±0.0033</v>
+      </c>
       <c r="E19" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
-        <v>0.9593±0.0033</v>
+        <f t="shared" ref="E19:J19" si="2" xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
+        <v>0.9436±0.0043</v>
       </c>
       <c r="F19" t="str">
-        <f t="shared" ref="F19:K19" si="2" xml:space="preserve"> TEXT(AVERAGE(F14:F18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F14:F18),"0.0000")</f>
-        <v>0.9436±0.0043</v>
+        <f t="shared" si="2"/>
+        <v>0.9437±0.0042</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="2"/>
-        <v>0.9437±0.0042</v>
+        <v>0.8707±0.0166</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" si="2"/>
-        <v>0.8707±0.0166</v>
+        <v>0.8433±0.0396</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" si="2"/>
-        <v>0.8433±0.0396</v>
+        <v>0.8867±0.0097</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="2"/>
-        <v>0.8867±0.0097</v>
-      </c>
-      <c r="K19" t="str">
-        <f t="shared" si="2"/>
         <v>0.8561±0.0161</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1">
         <v>42</v>
       </c>
       <c r="D20" s="4">
-        <v>26</v>
+        <v>0.96130000000000004</v>
       </c>
       <c r="E20" s="4">
-        <v>0.96130000000000004</v>
+        <v>0.90110000000000001</v>
       </c>
       <c r="F20" s="4">
-        <v>0.90110000000000001</v>
+        <v>0.90200000000000002</v>
       </c>
       <c r="G20" s="4">
-        <v>0.90200000000000002</v>
+        <v>0.74239999999999995</v>
       </c>
       <c r="H20" s="4">
-        <v>0.74239999999999995</v>
+        <v>0.875</v>
       </c>
       <c r="I20" s="4">
-        <v>0.875</v>
+        <v>0.88990000000000002</v>
       </c>
       <c r="J20" s="4">
-        <v>0.88990000000000002</v>
-      </c>
-      <c r="K20" s="4">
         <v>0.80330000000000001</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1">
         <v>1234</v>
       </c>
       <c r="D21" s="4">
-        <v>29</v>
+        <v>0.96960000000000002</v>
       </c>
       <c r="E21" s="4">
-        <v>0.96960000000000002</v>
+        <v>0.91210000000000002</v>
       </c>
       <c r="F21" s="4">
-        <v>0.91210000000000002</v>
+        <v>0.91300000000000003</v>
       </c>
       <c r="G21" s="4">
-        <v>0.91300000000000003</v>
+        <v>0.77610000000000001</v>
       </c>
       <c r="H21" s="4">
-        <v>0.77610000000000001</v>
+        <v>0.92859999999999998</v>
       </c>
       <c r="I21" s="4">
-        <v>0.92859999999999998</v>
+        <v>0.91279999999999994</v>
       </c>
       <c r="J21" s="4">
-        <v>0.91279999999999994</v>
-      </c>
-      <c r="K21" s="4">
         <v>0.84550000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="1">
         <v>2025</v>
       </c>
       <c r="D22" s="4">
-        <v>30</v>
+        <v>0.96319999999999995</v>
       </c>
       <c r="E22" s="4">
-        <v>0.96319999999999995</v>
+        <v>0.90239999999999998</v>
       </c>
       <c r="F22" s="4">
-        <v>0.90239999999999998</v>
+        <v>0.90369999999999995</v>
       </c>
       <c r="G22" s="4">
-        <v>0.90369999999999995</v>
+        <v>0.78459999999999996</v>
       </c>
       <c r="H22" s="4">
-        <v>0.78459999999999996</v>
+        <v>0.91069999999999995</v>
       </c>
       <c r="I22" s="4">
-        <v>0.91069999999999995</v>
+        <v>0.91279999999999994</v>
       </c>
       <c r="J22" s="4">
-        <v>0.91279999999999994</v>
-      </c>
-      <c r="K22" s="4">
         <v>0.84299999999999997</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1">
         <v>12345</v>
       </c>
       <c r="D23" s="4">
-        <v>27</v>
+        <v>0.97440000000000004</v>
       </c>
       <c r="E23" s="4">
-        <v>0.97440000000000004</v>
+        <v>0.89780000000000004</v>
       </c>
       <c r="F23" s="4">
-        <v>0.89780000000000004</v>
+        <v>0.90049999999999997</v>
       </c>
       <c r="G23" s="4">
-        <v>0.90049999999999997</v>
+        <v>0.91669999999999996</v>
       </c>
       <c r="H23" s="4">
-        <v>0.91669999999999996</v>
+        <v>0.78569999999999995</v>
       </c>
       <c r="I23" s="4">
-        <v>0.78569999999999995</v>
+        <v>0.92659999999999998</v>
       </c>
       <c r="J23" s="4">
-        <v>0.92659999999999998</v>
-      </c>
-      <c r="K23" s="4">
         <v>0.84609999999999996</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1">
         <v>666</v>
       </c>
       <c r="D24" s="4">
-        <v>20</v>
+        <v>0.96650000000000003</v>
       </c>
       <c r="E24" s="4">
-        <v>0.96650000000000003</v>
+        <v>0.88660000000000005</v>
       </c>
       <c r="F24" s="4">
-        <v>0.88660000000000005</v>
+        <v>0.88849999999999996</v>
       </c>
       <c r="G24" s="4">
-        <v>0.88849999999999996</v>
+        <v>0.86670000000000003</v>
       </c>
       <c r="H24" s="4">
-        <v>0.86670000000000003</v>
+        <v>0.69640000000000002</v>
       </c>
       <c r="I24" s="4">
-        <v>0.69640000000000002</v>
+        <v>0.89449999999999996</v>
       </c>
       <c r="J24" s="4">
-        <v>0.89449999999999996</v>
-      </c>
-      <c r="K24" s="4">
         <v>0.77229999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="D25" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D20:D24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D20:D24),"0.0000")</f>
+        <v>0.9670±0.0052</v>
+      </c>
       <c r="E25" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
-        <v>0.9670±0.0052</v>
+        <f t="shared" ref="E25:J25" si="3" xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
+        <v>0.9000±0.0092</v>
       </c>
       <c r="F25" t="str">
-        <f t="shared" ref="F25:K25" si="3" xml:space="preserve"> TEXT(AVERAGE(F20:F24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F20:F24),"0.0000")</f>
-        <v>0.9000±0.0092</v>
+        <f t="shared" si="3"/>
+        <v>0.9015±0.0088</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9015±0.0088</v>
+        <v>0.8173±0.0719</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8173±0.0719</v>
+        <v>0.8393±0.0970</v>
       </c>
       <c r="I25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8393±0.0970</v>
+        <v>0.9073±0.0150</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9073±0.0150</v>
-      </c>
-      <c r="K25" t="str">
-        <f t="shared" si="3"/>
         <v>0.8220±0.0331</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>42</v>
       </c>
       <c r="D26" s="4">
-        <v>29</v>
+        <v>0.97789999999999999</v>
       </c>
       <c r="E26" s="4">
-        <v>0.97789999999999999</v>
+        <v>0.98529999999999995</v>
       </c>
       <c r="F26" s="4">
         <v>0.98529999999999995</v>
       </c>
       <c r="G26" s="4">
-        <v>0.98529999999999995</v>
+        <v>0.94389999999999996</v>
       </c>
       <c r="H26" s="4">
-        <v>0.94389999999999996</v>
+        <v>0.9536</v>
       </c>
       <c r="I26" s="4">
-        <v>0.9536</v>
+        <v>0.93689999999999996</v>
       </c>
       <c r="J26" s="4">
-        <v>0.93689999999999996</v>
-      </c>
-      <c r="K26" s="4">
         <v>0.94869999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C27" s="1">
         <v>1234</v>
       </c>
       <c r="D27" s="4">
-        <v>30</v>
+        <v>0.97509999999999997</v>
       </c>
       <c r="E27" s="4">
-        <v>0.97509999999999997</v>
+        <v>0.98350000000000004</v>
       </c>
       <c r="F27" s="4">
-        <v>0.98350000000000004</v>
+        <v>0.98360000000000003</v>
       </c>
       <c r="G27" s="4">
-        <v>0.98360000000000003</v>
+        <v>0.92630000000000001</v>
       </c>
       <c r="H27" s="4">
-        <v>0.92630000000000001</v>
+        <v>0.90720000000000001</v>
       </c>
       <c r="I27" s="4">
-        <v>0.90720000000000001</v>
+        <v>0.89910000000000001</v>
       </c>
       <c r="J27" s="4">
-        <v>0.89910000000000001</v>
-      </c>
-      <c r="K27" s="4">
         <v>0.91669999999999996</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1">
         <v>2025</v>
       </c>
       <c r="D28" s="4">
-        <v>29</v>
+        <v>0.96850000000000003</v>
       </c>
       <c r="E28" s="4">
-        <v>0.96850000000000003</v>
+        <v>0.97819999999999996</v>
       </c>
       <c r="F28" s="4">
         <v>0.97819999999999996</v>
       </c>
       <c r="G28" s="4">
-        <v>0.97819999999999996</v>
+        <v>0.94920000000000004</v>
       </c>
       <c r="H28" s="4">
-        <v>0.94920000000000004</v>
+        <v>0.86599999999999999</v>
       </c>
       <c r="I28" s="4">
-        <v>0.86599999999999999</v>
+        <v>0.88959999999999995</v>
       </c>
       <c r="J28" s="4">
-        <v>0.88959999999999995</v>
-      </c>
-      <c r="K28" s="4">
         <v>0.90569999999999995</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" s="1">
         <v>12345</v>
       </c>
       <c r="D29" s="4">
-        <v>29</v>
+        <v>0.9788</v>
       </c>
       <c r="E29" s="4">
-        <v>0.9788</v>
+        <v>0.98640000000000005</v>
       </c>
       <c r="F29" s="4">
-        <v>0.98640000000000005</v>
+        <v>0.98650000000000004</v>
       </c>
       <c r="G29" s="4">
-        <v>0.98650000000000004</v>
+        <v>0.9204</v>
       </c>
       <c r="H29" s="4">
-        <v>0.9204</v>
+        <v>0.9536</v>
       </c>
       <c r="I29" s="4">
-        <v>0.9536</v>
+        <v>0.92110000000000003</v>
       </c>
       <c r="J29" s="4">
-        <v>0.92110000000000003</v>
-      </c>
-      <c r="K29" s="4">
         <v>0.93669999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" s="2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" s="1">
         <v>666</v>
       </c>
       <c r="D30" s="4">
-        <v>30</v>
+        <v>0.97130000000000005</v>
       </c>
       <c r="E30" s="4">
-        <v>0.97130000000000005</v>
+        <v>0.98</v>
       </c>
       <c r="F30" s="4">
         <v>0.98</v>
       </c>
       <c r="G30" s="4">
-        <v>0.98</v>
+        <v>0.91369999999999996</v>
       </c>
       <c r="H30" s="4">
-        <v>0.91369999999999996</v>
+        <v>0.92779999999999996</v>
       </c>
       <c r="I30" s="4">
-        <v>0.92779999999999996</v>
+        <v>0.9022</v>
       </c>
       <c r="J30" s="4">
-        <v>0.9022</v>
-      </c>
-      <c r="K30" s="4">
         <v>0.92069999999999996</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D31" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D26:D30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D26:D30),"0.0000")</f>
+        <v>0.9743±0.0044</v>
+      </c>
       <c r="E31" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
-        <v>0.9743±0.0044</v>
+        <f t="shared" ref="E31:J31" si="4" xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
+        <v>0.9827±0.0035</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" ref="F31:K31" si="4" xml:space="preserve"> TEXT(AVERAGE(F26:F30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F26:F30),"0.0000")</f>
+        <f t="shared" si="4"/>
         <v>0.9827±0.0035</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9827±0.0035</v>
+        <v>0.9307±0.0153</v>
       </c>
       <c r="H31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9307±0.0153</v>
+        <v>0.9216±0.0367</v>
       </c>
       <c r="I31" t="str">
         <f t="shared" si="4"/>
-        <v>0.9216±0.0367</v>
+        <v>0.9098±0.0190</v>
       </c>
       <c r="J31" t="str">
-        <f t="shared" si="4"/>
-        <v>0.9098±0.0190</v>
-      </c>
-      <c r="K31" t="str">
         <f t="shared" si="4"/>
         <v>0.9257±0.0170</v>
       </c>
@@ -3666,9 +3499,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2BA5AEE6-AEDC-49AA-B1CC-464D1D19E892}">
   <dimension ref="A1:L31"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3699,1072 +3532,990 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1">
         <v>42</v>
       </c>
       <c r="D2" s="4">
-        <v>29</v>
+        <v>0.85260000000000002</v>
       </c>
       <c r="E2" s="4">
-        <v>0.85260000000000002</v>
+        <v>0.83950000000000002</v>
       </c>
       <c r="F2" s="4">
-        <v>0.83950000000000002</v>
+        <v>0.84</v>
       </c>
       <c r="G2" s="4">
-        <v>0.84</v>
+        <v>0.7389</v>
       </c>
       <c r="H2" s="4">
-        <v>0.7389</v>
+        <v>0.78949999999999998</v>
       </c>
       <c r="I2" s="4">
-        <v>0.78949999999999998</v>
+        <v>0.76749999999999996</v>
       </c>
       <c r="J2" s="4">
-        <v>0.76749999999999996</v>
-      </c>
-      <c r="K2" s="4">
         <v>0.76339999999999997</v>
       </c>
       <c r="L2" s="4"/>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>1234</v>
       </c>
       <c r="D3" s="4">
-        <v>30</v>
+        <v>0.87419999999999998</v>
       </c>
       <c r="E3" s="4">
-        <v>0.87419999999999998</v>
+        <v>0.86839999999999995</v>
       </c>
       <c r="F3" s="4">
-        <v>0.86839999999999995</v>
+        <v>0.86870000000000003</v>
       </c>
       <c r="G3" s="4">
-        <v>0.86870000000000003</v>
+        <v>0.76719999999999999</v>
       </c>
       <c r="H3" s="4">
-        <v>0.76719999999999999</v>
+        <v>0.82369999999999999</v>
       </c>
       <c r="I3" s="4">
-        <v>0.82369999999999999</v>
+        <v>0.79749999999999999</v>
       </c>
       <c r="J3" s="4">
-        <v>0.79749999999999999</v>
-      </c>
-      <c r="K3" s="4">
         <v>0.7944</v>
       </c>
       <c r="L3" s="4"/>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
       </c>
       <c r="D4" s="4">
-        <v>30</v>
+        <v>0.8679</v>
       </c>
       <c r="E4" s="4">
-        <v>0.8679</v>
+        <v>0.84470000000000001</v>
       </c>
       <c r="F4" s="4">
-        <v>0.84470000000000001</v>
+        <v>0.84519999999999995</v>
       </c>
       <c r="G4" s="4">
-        <v>0.84519999999999995</v>
+        <v>0.74880000000000002</v>
       </c>
       <c r="H4" s="4">
-        <v>0.74880000000000002</v>
+        <v>0.84740000000000004</v>
       </c>
       <c r="I4" s="4">
-        <v>0.84740000000000004</v>
+        <v>0.79249999999999998</v>
       </c>
       <c r="J4" s="4">
-        <v>0.79249999999999998</v>
-      </c>
-      <c r="K4" s="4">
         <v>0.79510000000000003</v>
       </c>
       <c r="L4" s="4"/>
     </row>
-    <row r="5" spans="1:12">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1">
         <v>12345</v>
       </c>
       <c r="D5" s="4">
-        <v>30</v>
+        <v>0.85840000000000005</v>
       </c>
       <c r="E5" s="4">
-        <v>0.85840000000000005</v>
+        <v>0.83779999999999999</v>
       </c>
       <c r="F5" s="4">
-        <v>0.83779999999999999</v>
+        <v>0.83809999999999996</v>
       </c>
       <c r="G5" s="4">
-        <v>0.83809999999999996</v>
+        <v>0.72929999999999995</v>
       </c>
       <c r="H5" s="4">
-        <v>0.72929999999999995</v>
+        <v>0.8579</v>
       </c>
       <c r="I5" s="4">
-        <v>0.8579</v>
+        <v>0.78120000000000001</v>
       </c>
       <c r="J5" s="4">
-        <v>0.78120000000000001</v>
-      </c>
-      <c r="K5" s="4">
         <v>0.78839999999999999</v>
       </c>
       <c r="L5" s="4"/>
     </row>
-    <row r="6" spans="1:12">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1">
         <v>666</v>
       </c>
       <c r="D6" s="4">
-        <v>30</v>
+        <v>0.86609999999999998</v>
       </c>
       <c r="E6" s="4">
-        <v>0.86609999999999998</v>
+        <v>0.85019999999999996</v>
       </c>
       <c r="F6" s="4">
-        <v>0.85019999999999996</v>
+        <v>0.85060000000000002</v>
       </c>
       <c r="G6" s="4">
-        <v>0.85060000000000002</v>
+        <v>0.77639999999999998</v>
       </c>
       <c r="H6" s="4">
-        <v>0.77639999999999998</v>
+        <v>0.81320000000000003</v>
       </c>
       <c r="I6" s="4">
-        <v>0.81320000000000003</v>
+        <v>0.8</v>
       </c>
       <c r="J6" s="4">
-        <v>0.8</v>
-      </c>
-      <c r="K6" s="4">
         <v>0.79430000000000001</v>
       </c>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:12">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="D7" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D2:D6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D2:D6),"0.0000")</f>
+        <v>0.8638±0.0084</v>
+      </c>
       <c r="E7" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
-        <v>0.8638±0.0084</v>
+        <f t="shared" ref="E7:J7" si="0" xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
+        <v>0.8481±0.0123</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" ref="F7:K7" si="0" xml:space="preserve"> TEXT(AVERAGE(F2:F6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F2:F6),"0.0000")</f>
-        <v>0.8481±0.0123</v>
+        <f t="shared" si="0"/>
+        <v>0.8485±0.0123</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
-        <v>0.8485±0.0123</v>
+        <v>0.7521±0.0195</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
-        <v>0.7521±0.0195</v>
+        <v>0.8263±0.0273</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
-        <v>0.8263±0.0273</v>
+        <v>0.7877±0.0134</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>0.7877±0.0134</v>
-      </c>
-      <c r="K7" t="str">
-        <f t="shared" si="0"/>
         <v>0.7871±0.0135</v>
       </c>
     </row>
-    <row r="8" spans="1:12">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>42</v>
       </c>
       <c r="D8" s="4">
-        <v>30</v>
+        <v>0.84519999999999995</v>
       </c>
       <c r="E8" s="4">
-        <v>0.84519999999999995</v>
+        <v>0.86150000000000004</v>
       </c>
       <c r="F8" s="4">
-        <v>0.86150000000000004</v>
+        <v>0.86160000000000003</v>
       </c>
       <c r="G8" s="4">
-        <v>0.86160000000000003</v>
+        <v>0.74690000000000001</v>
       </c>
       <c r="H8" s="4">
-        <v>0.74690000000000001</v>
+        <v>0.79139999999999999</v>
       </c>
       <c r="I8" s="4">
-        <v>0.79139999999999999</v>
+        <v>0.76349999999999996</v>
       </c>
       <c r="J8" s="4">
-        <v>0.76349999999999996</v>
-      </c>
-      <c r="K8" s="4">
         <v>0.76849999999999996</v>
       </c>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:12">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>1234</v>
       </c>
       <c r="D9" s="4">
-        <v>30</v>
+        <v>0.85209999999999997</v>
       </c>
       <c r="E9" s="4">
-        <v>0.85209999999999997</v>
+        <v>0.8609</v>
       </c>
       <c r="F9" s="4">
-        <v>0.8609</v>
+        <v>0.86099999999999999</v>
       </c>
       <c r="G9" s="4">
-        <v>0.86099999999999999</v>
+        <v>0.79059999999999997</v>
       </c>
       <c r="H9" s="4">
-        <v>0.79059999999999997</v>
+        <v>0.76039999999999996</v>
       </c>
       <c r="I9" s="4">
-        <v>0.76039999999999996</v>
+        <v>0.78120000000000001</v>
       </c>
       <c r="J9" s="4">
-        <v>0.78120000000000001</v>
-      </c>
-      <c r="K9" s="4">
         <v>0.7752</v>
       </c>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:12">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1">
         <v>2025</v>
       </c>
       <c r="D10" s="4">
-        <v>29</v>
+        <v>0.8407</v>
       </c>
       <c r="E10" s="4">
-        <v>0.8407</v>
+        <v>0.85050000000000003</v>
       </c>
       <c r="F10" s="4">
-        <v>0.85050000000000003</v>
+        <v>0.85060000000000002</v>
       </c>
       <c r="G10" s="4">
-        <v>0.85060000000000002</v>
+        <v>0.79269999999999996</v>
       </c>
       <c r="H10" s="4">
-        <v>0.79269999999999996</v>
+        <v>0.72940000000000005</v>
       </c>
       <c r="I10" s="4">
-        <v>0.72940000000000005</v>
+        <v>0.77110000000000001</v>
       </c>
       <c r="J10" s="4">
-        <v>0.77110000000000001</v>
-      </c>
-      <c r="K10" s="4">
         <v>0.75980000000000003</v>
       </c>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:12">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>12345</v>
       </c>
       <c r="D11" s="4">
-        <v>30</v>
+        <v>0.83530000000000004</v>
       </c>
       <c r="E11" s="4">
-        <v>0.83530000000000004</v>
+        <v>0.83350000000000002</v>
       </c>
       <c r="F11" s="4">
-        <v>0.83350000000000002</v>
+        <v>0.8337</v>
       </c>
       <c r="G11" s="4">
-        <v>0.8337</v>
+        <v>0.71640000000000004</v>
       </c>
       <c r="H11" s="4">
-        <v>0.71640000000000004</v>
+        <v>0.81879999999999997</v>
       </c>
       <c r="I11" s="4">
-        <v>0.81879999999999997</v>
+        <v>0.74929999999999997</v>
       </c>
       <c r="J11" s="4">
-        <v>0.74929999999999997</v>
-      </c>
-      <c r="K11" s="4">
         <v>0.76419999999999999</v>
       </c>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:12">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
         <v>666</v>
       </c>
       <c r="D12" s="4">
-        <v>30</v>
+        <v>0.84409999999999996</v>
       </c>
       <c r="E12" s="4">
-        <v>0.84409999999999996</v>
+        <v>0.85309999999999997</v>
       </c>
       <c r="F12" s="4">
-        <v>0.85309999999999997</v>
+        <v>0.85329999999999995</v>
       </c>
       <c r="G12" s="4">
-        <v>0.85329999999999995</v>
+        <v>0.76880000000000004</v>
       </c>
       <c r="H12" s="4">
         <v>0.76880000000000004</v>
       </c>
       <c r="I12" s="4">
+        <v>0.77049999999999996</v>
+      </c>
+      <c r="J12" s="4">
         <v>0.76880000000000004</v>
       </c>
-      <c r="J12" s="4">
-        <v>0.77049999999999996</v>
-      </c>
-      <c r="K12" s="4">
-        <v>0.76880000000000004</v>
-      </c>
       <c r="L12" s="4"/>
     </row>
-    <row r="13" spans="1:12">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="D13" t="str">
+        <f t="shared" ref="D13:J13" si="1" xml:space="preserve"> TEXT(AVERAGE(D8:D12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D8:D12),"0.0000")</f>
+        <v>0.8435±0.0062</v>
+      </c>
       <c r="E13" t="str">
-        <f t="shared" ref="E13:K13" si="1" xml:space="preserve"> TEXT(AVERAGE(E8:E12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E8:E12),"0.0000")</f>
-        <v>0.8435±0.0062</v>
+        <f t="shared" si="1"/>
+        <v>0.8519±0.0113</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8519±0.0113</v>
+        <v>0.8520±0.0113</v>
       </c>
       <c r="G13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8520±0.0113</v>
+        <v>0.7631±0.0320</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="1"/>
-        <v>0.7631±0.0320</v>
+        <v>0.7738±0.0336</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="1"/>
-        <v>0.7738±0.0336</v>
+        <v>0.7671±0.0118</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
-        <v>0.7671±0.0118</v>
-      </c>
-      <c r="K13" t="str">
-        <f t="shared" si="1"/>
         <v>0.7673±0.0057</v>
       </c>
     </row>
-    <row r="14" spans="1:12">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1">
         <v>42</v>
       </c>
       <c r="D14" s="4">
-        <v>16</v>
+        <v>0.73219999999999996</v>
       </c>
       <c r="E14" s="4">
-        <v>0.73219999999999996</v>
+        <v>0.79279999999999995</v>
       </c>
       <c r="F14" s="4">
-        <v>0.79279999999999995</v>
+        <v>0.79300000000000004</v>
       </c>
       <c r="G14" s="4">
-        <v>0.79300000000000004</v>
+        <v>0.76670000000000005</v>
       </c>
       <c r="H14" s="4">
-        <v>0.76670000000000005</v>
+        <v>0.62290000000000001</v>
       </c>
       <c r="I14" s="4">
-        <v>0.62290000000000001</v>
+        <v>0.6714</v>
       </c>
       <c r="J14" s="4">
-        <v>0.6714</v>
-      </c>
-      <c r="K14" s="4">
         <v>0.68740000000000001</v>
       </c>
       <c r="L14" s="4"/>
     </row>
-    <row r="15" spans="1:12">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1">
         <v>1234</v>
       </c>
       <c r="D15" s="4">
-        <v>8</v>
+        <v>0.72099999999999997</v>
       </c>
       <c r="E15" s="4">
-        <v>0.72099999999999997</v>
+        <v>0.77459999999999996</v>
       </c>
       <c r="F15" s="4">
-        <v>0.77459999999999996</v>
+        <v>0.77480000000000004</v>
       </c>
       <c r="G15" s="4">
-        <v>0.77480000000000004</v>
+        <v>0.75580000000000003</v>
       </c>
       <c r="H15" s="4">
-        <v>0.75580000000000003</v>
+        <v>0.58050000000000002</v>
       </c>
       <c r="I15" s="4">
-        <v>0.58050000000000002</v>
+        <v>0.64800000000000002</v>
       </c>
       <c r="J15" s="4">
-        <v>0.64800000000000002</v>
-      </c>
-      <c r="K15" s="4">
         <v>0.65659999999999996</v>
       </c>
       <c r="L15" s="4"/>
     </row>
-    <row r="16" spans="1:12">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1">
         <v>2025</v>
       </c>
       <c r="D16" s="4">
-        <v>19</v>
+        <v>0.69599999999999995</v>
       </c>
       <c r="E16" s="4">
-        <v>0.69599999999999995</v>
+        <v>0.78</v>
       </c>
       <c r="F16" s="4">
-        <v>0.78</v>
+        <v>0.7802</v>
       </c>
       <c r="G16" s="4">
-        <v>0.7802</v>
+        <v>0.71960000000000002</v>
       </c>
       <c r="H16" s="4">
-        <v>0.71960000000000002</v>
+        <v>0.63570000000000004</v>
       </c>
       <c r="I16" s="4">
-        <v>0.63570000000000004</v>
+        <v>0.64510000000000001</v>
       </c>
       <c r="J16" s="4">
-        <v>0.64510000000000001</v>
-      </c>
-      <c r="K16" s="4">
         <v>0.67500000000000004</v>
       </c>
       <c r="L16" s="4"/>
     </row>
-    <row r="17" spans="1:12">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1">
         <v>12345</v>
       </c>
       <c r="D17" s="4">
-        <v>10</v>
+        <v>0.72040000000000004</v>
       </c>
       <c r="E17" s="4">
-        <v>0.72040000000000004</v>
+        <v>0.78090000000000004</v>
       </c>
       <c r="F17" s="4">
-        <v>0.78090000000000004</v>
+        <v>0.78100000000000003</v>
       </c>
       <c r="G17" s="4">
-        <v>0.78100000000000003</v>
+        <v>0.75719999999999998</v>
       </c>
       <c r="H17" s="4">
-        <v>0.75719999999999998</v>
+        <v>0.54790000000000005</v>
       </c>
       <c r="I17" s="4">
-        <v>0.54790000000000005</v>
+        <v>0.63590000000000002</v>
       </c>
       <c r="J17" s="4">
-        <v>0.63590000000000002</v>
-      </c>
-      <c r="K17" s="4">
         <v>0.63570000000000004</v>
       </c>
       <c r="L17" s="4"/>
     </row>
-    <row r="18" spans="1:12">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1">
         <v>666</v>
       </c>
       <c r="D18" s="4">
-        <v>15</v>
+        <v>0.73880000000000001</v>
       </c>
       <c r="E18" s="4">
-        <v>0.73880000000000001</v>
+        <v>0.80349999999999999</v>
       </c>
       <c r="F18" s="4">
-        <v>0.80349999999999999</v>
+        <v>0.80359999999999998</v>
       </c>
       <c r="G18" s="4">
-        <v>0.80359999999999998</v>
+        <v>0.77759999999999996</v>
       </c>
       <c r="H18" s="4">
-        <v>0.77759999999999996</v>
+        <v>0.60409999999999997</v>
       </c>
       <c r="I18" s="4">
-        <v>0.60409999999999997</v>
+        <v>0.67030000000000001</v>
       </c>
       <c r="J18" s="4">
-        <v>0.67030000000000001</v>
-      </c>
-      <c r="K18" s="4">
         <v>0.68</v>
       </c>
       <c r="L18" s="4"/>
     </row>
-    <row r="19" spans="1:12">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="D19" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D14:D18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D14:D18),"0.0000")</f>
+        <v>0.7217±0.0163</v>
+      </c>
       <c r="E19" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
-        <v>0.7217±0.0163</v>
+        <f t="shared" ref="E19:J19" si="2" xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
+        <v>0.7864±0.0117</v>
       </c>
       <c r="F19" t="str">
-        <f t="shared" ref="F19:K19" si="2" xml:space="preserve"> TEXT(AVERAGE(F14:F18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F14:F18),"0.0000")</f>
-        <v>0.7864±0.0117</v>
+        <f t="shared" si="2"/>
+        <v>0.7865±0.0116</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="2"/>
-        <v>0.7865±0.0116</v>
+        <v>0.7554±0.0218</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" si="2"/>
-        <v>0.7554±0.0218</v>
+        <v>0.5982±0.0350</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" si="2"/>
-        <v>0.5982±0.0350</v>
+        <v>0.6541±0.0159</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="2"/>
-        <v>0.6541±0.0159</v>
-      </c>
-      <c r="K19" t="str">
-        <f t="shared" si="2"/>
         <v>0.6669±0.0208</v>
       </c>
     </row>
-    <row r="20" spans="1:12">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1">
         <v>42</v>
       </c>
       <c r="D20" s="4">
-        <v>30</v>
+        <v>0.82020000000000004</v>
       </c>
       <c r="E20" s="4">
-        <v>0.82020000000000004</v>
+        <v>0.81440000000000001</v>
       </c>
       <c r="F20" s="4">
-        <v>0.81440000000000001</v>
+        <v>0.81510000000000005</v>
       </c>
       <c r="G20" s="4">
-        <v>0.81510000000000005</v>
+        <v>0.79490000000000005</v>
       </c>
       <c r="H20" s="4">
-        <v>0.79490000000000005</v>
+        <v>0.62839999999999996</v>
       </c>
       <c r="I20" s="4">
-        <v>0.62839999999999996</v>
+        <v>0.77029999999999998</v>
       </c>
       <c r="J20" s="4">
-        <v>0.77029999999999998</v>
-      </c>
-      <c r="K20" s="4">
         <v>0.70189999999999997</v>
       </c>
       <c r="L20" s="4"/>
     </row>
-    <row r="21" spans="1:12">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A21" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1">
         <v>1234</v>
       </c>
       <c r="D21" s="4">
-        <v>28</v>
+        <v>0.83130000000000004</v>
       </c>
       <c r="E21" s="4">
-        <v>0.83130000000000004</v>
+        <v>0.81699999999999995</v>
       </c>
       <c r="F21" s="4">
-        <v>0.81699999999999995</v>
+        <v>0.81769999999999998</v>
       </c>
       <c r="G21" s="4">
-        <v>0.81769999999999998</v>
+        <v>0.67459999999999998</v>
       </c>
       <c r="H21" s="4">
-        <v>0.67459999999999998</v>
+        <v>0.77029999999999998</v>
       </c>
       <c r="I21" s="4">
-        <v>0.77029999999999998</v>
+        <v>0.74129999999999996</v>
       </c>
       <c r="J21" s="4">
-        <v>0.74129999999999996</v>
-      </c>
-      <c r="K21" s="4">
         <v>0.71919999999999995</v>
       </c>
       <c r="L21" s="4"/>
     </row>
-    <row r="22" spans="1:12">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A22" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="1">
         <v>2025</v>
       </c>
       <c r="D22" s="4">
-        <v>29</v>
+        <v>0.8488</v>
       </c>
       <c r="E22" s="4">
-        <v>0.8488</v>
+        <v>0.83560000000000001</v>
       </c>
       <c r="F22" s="4">
-        <v>0.83560000000000001</v>
+        <v>0.83620000000000005</v>
       </c>
       <c r="G22" s="4">
-        <v>0.83620000000000005</v>
+        <v>0.68510000000000004</v>
       </c>
       <c r="H22" s="4">
-        <v>0.68510000000000004</v>
+        <v>0.83779999999999999</v>
       </c>
       <c r="I22" s="4">
-        <v>0.83779999999999999</v>
+        <v>0.76449999999999996</v>
       </c>
       <c r="J22" s="4">
-        <v>0.76449999999999996</v>
-      </c>
-      <c r="K22" s="4">
         <v>0.75380000000000003</v>
       </c>
       <c r="L22" s="4"/>
     </row>
-    <row r="23" spans="1:12">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1">
         <v>12345</v>
       </c>
       <c r="D23" s="4">
-        <v>27</v>
+        <v>0.84189999999999998</v>
       </c>
       <c r="E23" s="4">
-        <v>0.84189999999999998</v>
+        <v>0.82289999999999996</v>
       </c>
       <c r="F23" s="4">
-        <v>0.82289999999999996</v>
+        <v>0.8236</v>
       </c>
       <c r="G23" s="4">
-        <v>0.8236</v>
+        <v>0.75890000000000002</v>
       </c>
       <c r="H23" s="4">
-        <v>0.75890000000000002</v>
+        <v>0.72299999999999998</v>
       </c>
       <c r="I23" s="4">
-        <v>0.72299999999999998</v>
+        <v>0.78200000000000003</v>
       </c>
       <c r="J23" s="4">
-        <v>0.78200000000000003</v>
-      </c>
-      <c r="K23" s="4">
         <v>0.74050000000000005</v>
       </c>
       <c r="L23" s="4"/>
     </row>
-    <row r="24" spans="1:12">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1">
         <v>666</v>
       </c>
       <c r="D24" s="4">
-        <v>30</v>
+        <v>0.8427</v>
       </c>
       <c r="E24" s="4">
-        <v>0.8427</v>
+        <v>0.84009999999999996</v>
       </c>
       <c r="F24" s="4">
-        <v>0.84009999999999996</v>
+        <v>0.8407</v>
       </c>
       <c r="G24" s="4">
-        <v>0.8407</v>
+        <v>0.7278</v>
       </c>
       <c r="H24" s="4">
-        <v>0.7278</v>
+        <v>0.77700000000000002</v>
       </c>
       <c r="I24" s="4">
-        <v>0.77700000000000002</v>
+        <v>0.77910000000000001</v>
       </c>
       <c r="J24" s="4">
-        <v>0.77910000000000001</v>
-      </c>
-      <c r="K24" s="4">
         <v>0.75160000000000005</v>
       </c>
       <c r="L24" s="4"/>
     </row>
-    <row r="25" spans="1:12">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="D25" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D20:D24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D20:D24),"0.0000")</f>
+        <v>0.8370±0.0113</v>
+      </c>
       <c r="E25" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
-        <v>0.8370±0.0113</v>
+        <f t="shared" ref="E25:J25" si="3" xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
+        <v>0.8260±0.0114</v>
       </c>
       <c r="F25" t="str">
-        <f t="shared" ref="F25:K25" si="3" xml:space="preserve"> TEXT(AVERAGE(F20:F24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F20:F24),"0.0000")</f>
-        <v>0.8260±0.0114</v>
+        <f t="shared" si="3"/>
+        <v>0.8267±0.0113</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8267±0.0113</v>
+        <v>0.7283±0.0503</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" si="3"/>
-        <v>0.7283±0.0503</v>
+        <v>0.7473±0.0780</v>
       </c>
       <c r="I25" t="str">
         <f t="shared" si="3"/>
-        <v>0.7473±0.0780</v>
+        <v>0.7674±0.0162</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="3"/>
-        <v>0.7674±0.0162</v>
-      </c>
-      <c r="K25" t="str">
-        <f t="shared" si="3"/>
         <v>0.7334±0.0223</v>
       </c>
     </row>
-    <row r="26" spans="1:12">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A26" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>42</v>
       </c>
       <c r="D26" s="4">
-        <v>16</v>
+        <v>0.74580000000000002</v>
       </c>
       <c r="E26" s="4">
-        <v>0.74580000000000002</v>
+        <v>0.76349999999999996</v>
       </c>
       <c r="F26" s="4">
-        <v>0.76349999999999996</v>
+        <v>0.76490000000000002</v>
       </c>
       <c r="G26" s="4">
-        <v>0.76490000000000002</v>
+        <v>0.68420000000000003</v>
       </c>
       <c r="H26" s="4">
-        <v>0.68420000000000003</v>
+        <v>0.74590000000000001</v>
       </c>
       <c r="I26" s="4">
-        <v>0.74590000000000001</v>
+        <v>0.68530000000000002</v>
       </c>
       <c r="J26" s="4">
-        <v>0.68530000000000002</v>
-      </c>
-      <c r="K26" s="4">
         <v>0.7137</v>
       </c>
       <c r="L26" s="4"/>
     </row>
-    <row r="27" spans="1:12">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C27" s="1">
         <v>1234</v>
       </c>
       <c r="D27" s="4">
-        <v>9</v>
+        <v>0.74550000000000005</v>
       </c>
       <c r="E27" s="4">
-        <v>0.74550000000000005</v>
+        <v>0.77880000000000005</v>
       </c>
       <c r="F27" s="4">
-        <v>0.77880000000000005</v>
+        <v>0.78</v>
       </c>
       <c r="G27" s="4">
-        <v>0.78</v>
+        <v>0.60870000000000002</v>
       </c>
       <c r="H27" s="4">
-        <v>0.60870000000000002</v>
+        <v>0.80330000000000001</v>
       </c>
       <c r="I27" s="4">
-        <v>0.80330000000000001</v>
+        <v>0.625</v>
       </c>
       <c r="J27" s="4">
-        <v>0.625</v>
-      </c>
-      <c r="K27" s="4">
         <v>0.69259999999999999</v>
       </c>
       <c r="L27" s="4"/>
     </row>
-    <row r="28" spans="1:12">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1">
         <v>2025</v>
       </c>
       <c r="D28" s="4">
-        <v>27</v>
+        <v>0.77039999999999997</v>
       </c>
       <c r="E28" s="4">
-        <v>0.77039999999999997</v>
+        <v>0.79579999999999995</v>
       </c>
       <c r="F28" s="4">
-        <v>0.79579999999999995</v>
+        <v>0.79690000000000005</v>
       </c>
       <c r="G28" s="4">
-        <v>0.79690000000000005</v>
+        <v>0.68669999999999998</v>
       </c>
       <c r="H28" s="4">
-        <v>0.68669999999999998</v>
+        <v>0.84430000000000005</v>
       </c>
       <c r="I28" s="4">
-        <v>0.84430000000000005</v>
+        <v>0.71550000000000002</v>
       </c>
       <c r="J28" s="4">
-        <v>0.71550000000000002</v>
-      </c>
-      <c r="K28" s="4">
         <v>0.75729999999999997</v>
       </c>
       <c r="L28" s="4"/>
     </row>
-    <row r="29" spans="1:12">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A29" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" s="1">
         <v>12345</v>
       </c>
       <c r="D29" s="4">
-        <v>13</v>
+        <v>0.73950000000000005</v>
       </c>
       <c r="E29" s="4">
-        <v>0.73950000000000005</v>
+        <v>0.75149999999999995</v>
       </c>
       <c r="F29" s="4">
-        <v>0.75149999999999995</v>
+        <v>0.754</v>
       </c>
       <c r="G29" s="4">
-        <v>0.754</v>
+        <v>0.65580000000000005</v>
       </c>
       <c r="H29" s="4">
-        <v>0.65580000000000005</v>
+        <v>0.82789999999999997</v>
       </c>
       <c r="I29" s="4">
-        <v>0.82789999999999997</v>
+        <v>0.68100000000000005</v>
       </c>
       <c r="J29" s="4">
-        <v>0.68100000000000005</v>
-      </c>
-      <c r="K29" s="4">
         <v>0.7319</v>
       </c>
       <c r="L29" s="4"/>
     </row>
-    <row r="30" spans="1:12">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
       <c r="A30" s="3" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" s="1">
         <v>666</v>
       </c>
       <c r="D30" s="4">
-        <v>23</v>
+        <v>0.7671</v>
       </c>
       <c r="E30" s="4">
-        <v>0.7671</v>
+        <v>0.8125</v>
       </c>
       <c r="F30" s="4">
-        <v>0.8125</v>
+        <v>0.81340000000000001</v>
       </c>
       <c r="G30" s="4">
-        <v>0.81340000000000001</v>
+        <v>0.60919999999999996</v>
       </c>
       <c r="H30" s="4">
-        <v>0.60919999999999996</v>
+        <v>0.86890000000000001</v>
       </c>
       <c r="I30" s="4">
-        <v>0.86890000000000001</v>
+        <v>0.63790000000000002</v>
       </c>
       <c r="J30" s="4">
-        <v>0.63790000000000002</v>
-      </c>
-      <c r="K30" s="4">
         <v>0.71619999999999995</v>
       </c>
       <c r="L30" s="4"/>
     </row>
-    <row r="31" spans="1:12">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="D31" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D26:D30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D26:D30),"0.0000")</f>
+        <v>0.7537±0.0141</v>
+      </c>
       <c r="E31" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
-        <v>0.7537±0.0141</v>
+        <f t="shared" ref="E31:J31" si="4" xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
+        <v>0.7804±0.0244</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" ref="F31:K31" si="4" xml:space="preserve"> TEXT(AVERAGE(F26:F30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F26:F30),"0.0000")</f>
-        <v>0.7804±0.0244</v>
+        <f t="shared" si="4"/>
+        <v>0.7818±0.0239</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="4"/>
-        <v>0.7818±0.0239</v>
+        <v>0.6489±0.0385</v>
       </c>
       <c r="H31" t="str">
         <f t="shared" si="4"/>
-        <v>0.6489±0.0385</v>
+        <v>0.8181±0.0469</v>
       </c>
       <c r="I31" t="str">
         <f t="shared" si="4"/>
-        <v>0.8181±0.0469</v>
+        <v>0.6689±0.0370</v>
       </c>
       <c r="J31" t="str">
-        <f t="shared" si="4"/>
-        <v>0.6689±0.0370</v>
-      </c>
-      <c r="K31" t="str">
         <f t="shared" si="4"/>
         <v>0.7223±0.0240</v>
       </c>
@@ -4778,10 +4529,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45275180-57AC-4BB6-B1CC-6E162588BEA5}">
-  <dimension ref="A1:K31"/>
-  <sheetFormatPr defaultRowHeight="14.25"/>
+  <dimension ref="A1:J31"/>
+  <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4812,402 +4563,371 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A2" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C2" s="1">
         <v>42</v>
       </c>
       <c r="D2" s="4">
-        <v>30</v>
+        <v>0.93049999999999999</v>
       </c>
       <c r="E2" s="4">
-        <v>0.93049999999999999</v>
+        <v>0.92479999999999996</v>
       </c>
       <c r="F2" s="4">
-        <v>0.92479999999999996</v>
+        <v>0.92490000000000006</v>
       </c>
       <c r="G2" s="4">
-        <v>0.92490000000000006</v>
+        <v>0.78200000000000003</v>
       </c>
       <c r="H2" s="4">
-        <v>0.78200000000000003</v>
+        <v>0.92330000000000001</v>
       </c>
       <c r="I2" s="4">
-        <v>0.92330000000000001</v>
+        <v>0.84140000000000004</v>
       </c>
       <c r="J2" s="4">
-        <v>0.84140000000000004</v>
-      </c>
-      <c r="K2" s="4">
         <v>0.8468</v>
       </c>
     </row>
-    <row r="3" spans="1:11">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
         <v>1234</v>
       </c>
       <c r="D3" s="4">
-        <v>28</v>
+        <v>0.94330000000000003</v>
       </c>
       <c r="E3" s="4">
-        <v>0.94330000000000003</v>
+        <v>0.94</v>
       </c>
       <c r="F3" s="4">
-        <v>0.94</v>
+        <v>0.94010000000000005</v>
       </c>
       <c r="G3" s="4">
-        <v>0.94010000000000005</v>
+        <v>0.90480000000000005</v>
       </c>
       <c r="H3" s="4">
-        <v>0.90480000000000005</v>
+        <v>0.84650000000000003</v>
       </c>
       <c r="I3" s="4">
-        <v>0.84650000000000003</v>
+        <v>0.88480000000000003</v>
       </c>
       <c r="J3" s="4">
-        <v>0.88480000000000003</v>
-      </c>
-      <c r="K3" s="4">
         <v>0.87470000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:11">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A4" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1">
         <v>2025</v>
       </c>
       <c r="D4" s="4">
-        <v>30</v>
+        <v>0.94110000000000005</v>
       </c>
       <c r="E4" s="4">
-        <v>0.94110000000000005</v>
+        <v>0.94199999999999995</v>
       </c>
       <c r="F4" s="4">
         <v>0.94199999999999995</v>
       </c>
       <c r="G4" s="4">
-        <v>0.94199999999999995</v>
+        <v>0.88019999999999998</v>
       </c>
       <c r="H4" s="4">
-        <v>0.88019999999999998</v>
+        <v>0.83660000000000001</v>
       </c>
       <c r="I4" s="4">
-        <v>0.83660000000000001</v>
+        <v>0.86839999999999995</v>
       </c>
       <c r="J4" s="4">
-        <v>0.86839999999999995</v>
-      </c>
-      <c r="K4" s="4">
         <v>0.8579</v>
       </c>
     </row>
-    <row r="5" spans="1:11">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A5" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C5" s="1">
         <v>12345</v>
       </c>
       <c r="D5" s="4">
-        <v>30</v>
+        <v>0.93420000000000003</v>
       </c>
       <c r="E5" s="4">
-        <v>0.93420000000000003</v>
+        <v>0.93100000000000005</v>
       </c>
       <c r="F5" s="4">
-        <v>0.93100000000000005</v>
+        <v>0.93110000000000004</v>
       </c>
       <c r="G5" s="4">
-        <v>0.93110000000000004</v>
+        <v>0.81310000000000004</v>
       </c>
       <c r="H5" s="4">
-        <v>0.81310000000000004</v>
+        <v>0.89359999999999995</v>
       </c>
       <c r="I5" s="4">
-        <v>0.89359999999999995</v>
+        <v>0.85189999999999999</v>
       </c>
       <c r="J5" s="4">
-        <v>0.85189999999999999</v>
-      </c>
-      <c r="K5" s="4">
         <v>0.85140000000000005</v>
       </c>
     </row>
-    <row r="6" spans="1:11">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A6" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C6" s="1">
         <v>666</v>
       </c>
       <c r="D6" s="4">
-        <v>30</v>
+        <v>0.94499999999999995</v>
       </c>
       <c r="E6" s="4">
         <v>0.94499999999999995</v>
       </c>
       <c r="F6" s="4">
-        <v>0.94499999999999995</v>
+        <v>0.94510000000000005</v>
       </c>
       <c r="G6" s="4">
-        <v>0.94510000000000005</v>
+        <v>0.88660000000000005</v>
       </c>
       <c r="H6" s="4">
-        <v>0.88660000000000005</v>
+        <v>0.87129999999999996</v>
       </c>
       <c r="I6" s="4">
-        <v>0.87129999999999996</v>
+        <v>0.88600000000000001</v>
       </c>
       <c r="J6" s="4">
-        <v>0.88600000000000001</v>
-      </c>
-      <c r="K6" s="4">
         <v>0.87890000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:11">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A7" s="1"/>
       <c r="B7" s="1"/>
       <c r="C7" s="1"/>
-      <c r="D7" s="1"/>
+      <c r="D7" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D2:D6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D2:D6),"0.0000")</f>
+        <v>0.9388±0.0062</v>
+      </c>
       <c r="E7" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
-        <v>0.9388±0.0062</v>
+        <f t="shared" ref="E7:J7" si="0" xml:space="preserve"> TEXT(AVERAGE(E2:E6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E2:E6),"0.0000")</f>
+        <v>0.9366±0.0084</v>
       </c>
       <c r="F7" t="str">
-        <f t="shared" ref="F7:K7" si="0" xml:space="preserve"> TEXT(AVERAGE(F2:F6),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F2:F6),"0.0000")</f>
+        <f t="shared" si="0"/>
         <v>0.9366±0.0084</v>
       </c>
       <c r="G7" t="str">
         <f t="shared" si="0"/>
-        <v>0.9366±0.0084</v>
+        <v>0.8533±0.0529</v>
       </c>
       <c r="H7" t="str">
         <f t="shared" si="0"/>
-        <v>0.8533±0.0529</v>
+        <v>0.8743±0.0353</v>
       </c>
       <c r="I7" t="str">
         <f t="shared" si="0"/>
-        <v>0.8743±0.0353</v>
+        <v>0.8665±0.0198</v>
       </c>
       <c r="J7" t="str">
         <f t="shared" si="0"/>
-        <v>0.8665±0.0198</v>
-      </c>
-      <c r="K7" t="str">
-        <f t="shared" si="0"/>
         <v>0.8619±0.0142</v>
       </c>
     </row>
-    <row r="8" spans="1:11">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A8" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1">
         <v>42</v>
       </c>
       <c r="D8" s="4">
-        <v>29</v>
+        <v>0.93889999999999996</v>
       </c>
       <c r="E8" s="4">
-        <v>0.93889999999999996</v>
+        <v>0.93630000000000002</v>
       </c>
       <c r="F8" s="4">
-        <v>0.93630000000000002</v>
+        <v>0.93640000000000001</v>
       </c>
       <c r="G8" s="4">
-        <v>0.93640000000000001</v>
+        <v>0.85109999999999997</v>
       </c>
       <c r="H8" s="4">
-        <v>0.85109999999999997</v>
+        <v>0.87839999999999996</v>
       </c>
       <c r="I8" s="4">
-        <v>0.87839999999999996</v>
+        <v>0.8639</v>
       </c>
       <c r="J8" s="4">
-        <v>0.8639</v>
-      </c>
-      <c r="K8" s="4">
         <v>0.86460000000000004</v>
       </c>
     </row>
-    <row r="9" spans="1:11">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A9" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>1234</v>
       </c>
       <c r="D9" s="4">
-        <v>29</v>
+        <v>0.93089999999999995</v>
       </c>
       <c r="E9" s="4">
-        <v>0.93089999999999995</v>
+        <v>0.92159999999999997</v>
       </c>
       <c r="F9" s="4">
-        <v>0.92159999999999997</v>
+        <v>0.92169999999999996</v>
       </c>
       <c r="G9" s="4">
-        <v>0.92169999999999996</v>
+        <v>0.83509999999999995</v>
       </c>
       <c r="H9" s="4">
-        <v>0.83509999999999995</v>
+        <v>0.88880000000000003</v>
       </c>
       <c r="I9" s="4">
-        <v>0.88880000000000003</v>
+        <v>0.85829999999999995</v>
       </c>
       <c r="J9" s="4">
-        <v>0.85829999999999995</v>
-      </c>
-      <c r="K9" s="4">
         <v>0.86109999999999998</v>
       </c>
     </row>
-    <row r="10" spans="1:11">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A10" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C10" s="1">
         <v>2025</v>
       </c>
       <c r="D10" s="4">
-        <v>29</v>
+        <v>0.93679999999999997</v>
       </c>
       <c r="E10" s="4">
-        <v>0.93679999999999997</v>
+        <v>0.93300000000000005</v>
       </c>
       <c r="F10" s="4">
-        <v>0.93300000000000005</v>
+        <v>0.93310000000000004</v>
       </c>
       <c r="G10" s="4">
-        <v>0.93310000000000004</v>
+        <v>0.80779999999999996</v>
       </c>
       <c r="H10" s="4">
-        <v>0.80779999999999996</v>
+        <v>0.93</v>
       </c>
       <c r="I10" s="4">
-        <v>0.93</v>
+        <v>0.85599999999999998</v>
       </c>
       <c r="J10" s="4">
-        <v>0.85599999999999998</v>
-      </c>
-      <c r="K10" s="4">
         <v>0.86460000000000004</v>
       </c>
     </row>
-    <row r="11" spans="1:11">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A11" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C11" s="1">
         <v>12345</v>
       </c>
       <c r="D11" s="4">
-        <v>26</v>
+        <v>0.93400000000000005</v>
       </c>
       <c r="E11" s="4">
-        <v>0.93400000000000005</v>
+        <v>0.93369999999999997</v>
       </c>
       <c r="F11" s="4">
-        <v>0.93369999999999997</v>
+        <v>0.93379999999999996</v>
       </c>
       <c r="G11" s="4">
-        <v>0.93379999999999996</v>
+        <v>0.85729999999999995</v>
       </c>
       <c r="H11" s="4">
-        <v>0.85729999999999995</v>
+        <v>0.86119999999999997</v>
       </c>
       <c r="I11" s="4">
-        <v>0.86119999999999997</v>
+        <v>0.86050000000000004</v>
       </c>
       <c r="J11" s="4">
-        <v>0.86050000000000004</v>
-      </c>
-      <c r="K11" s="4">
         <v>0.85929999999999995</v>
       </c>
     </row>
-    <row r="12" spans="1:11">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A12" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C12" s="1">
         <v>666</v>
       </c>
       <c r="D12" s="4">
-        <v>28</v>
+        <v>0.93279999999999996</v>
       </c>
       <c r="E12" s="4">
-        <v>0.93279999999999996</v>
+        <v>0.92969999999999997</v>
       </c>
       <c r="F12" s="4">
         <v>0.92969999999999997</v>
       </c>
       <c r="G12" s="4">
-        <v>0.92969999999999997</v>
+        <v>0.80659999999999998</v>
       </c>
       <c r="H12" s="4">
-        <v>0.80659999999999998</v>
+        <v>0.90369999999999995</v>
       </c>
       <c r="I12" s="4">
-        <v>0.90369999999999995</v>
+        <v>0.84519999999999995</v>
       </c>
       <c r="J12" s="4">
-        <v>0.84519999999999995</v>
-      </c>
-      <c r="K12" s="4">
         <v>0.85229999999999995</v>
       </c>
     </row>
-    <row r="13" spans="1:11">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A13" s="1"/>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
-      <c r="D13" s="1"/>
+      <c r="D13" t="str">
+        <f t="shared" ref="D13:J13" si="1" xml:space="preserve"> TEXT(AVERAGE(D8:D12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D8:D12),"0.0000")</f>
+        <v>0.9347±0.0032</v>
+      </c>
       <c r="E13" t="str">
-        <f t="shared" ref="E13:K13" si="1" xml:space="preserve"> TEXT(AVERAGE(E8:E12),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E8:E12),"0.0000")</f>
-        <v>0.9347±0.0032</v>
+        <f t="shared" si="1"/>
+        <v>0.9309±0.0057</v>
       </c>
       <c r="F13" t="str">
         <f t="shared" si="1"/>
@@ -5215,644 +4935,593 @@
       </c>
       <c r="G13" t="str">
         <f t="shared" si="1"/>
-        <v>0.9309±0.0057</v>
+        <v>0.8316±0.0237</v>
       </c>
       <c r="H13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8316±0.0237</v>
+        <v>0.8924±0.0261</v>
       </c>
       <c r="I13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8924±0.0261</v>
+        <v>0.8568±0.0071</v>
       </c>
       <c r="J13" t="str">
         <f t="shared" si="1"/>
-        <v>0.8568±0.0071</v>
-      </c>
-      <c r="K13" t="str">
-        <f t="shared" si="1"/>
         <v>0.8604±0.0051</v>
       </c>
     </row>
-    <row r="14" spans="1:11">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A14" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C14" s="1">
         <v>42</v>
       </c>
       <c r="D14" s="4">
-        <v>21</v>
+        <v>0.55520000000000003</v>
       </c>
       <c r="E14" s="4">
-        <v>0.55520000000000003</v>
+        <v>0.63919999999999999</v>
       </c>
       <c r="F14" s="4">
-        <v>0.63919999999999999</v>
+        <v>0.63949999999999996</v>
       </c>
       <c r="G14" s="4">
-        <v>0.63949999999999996</v>
+        <v>0.55869999999999997</v>
       </c>
       <c r="H14" s="4">
-        <v>0.55869999999999997</v>
+        <v>0.65249999999999997</v>
       </c>
       <c r="I14" s="4">
-        <v>0.65249999999999997</v>
+        <v>0.52539999999999998</v>
       </c>
       <c r="J14" s="4">
-        <v>0.52539999999999998</v>
-      </c>
-      <c r="K14" s="4">
         <v>0.60199999999999998</v>
       </c>
     </row>
-    <row r="15" spans="1:11">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A15" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C15" s="1">
         <v>1234</v>
       </c>
       <c r="D15" s="4">
-        <v>28</v>
+        <v>0.56840000000000002</v>
       </c>
       <c r="E15" s="4">
-        <v>0.56840000000000002</v>
+        <v>0.62529999999999997</v>
       </c>
       <c r="F15" s="4">
-        <v>0.62529999999999997</v>
+        <v>0.62560000000000004</v>
       </c>
       <c r="G15" s="4">
-        <v>0.62560000000000004</v>
+        <v>0.59209999999999996</v>
       </c>
       <c r="H15" s="4">
-        <v>0.59209999999999996</v>
+        <v>0.82679999999999998</v>
       </c>
       <c r="I15" s="4">
-        <v>0.82679999999999998</v>
+        <v>0.59150000000000003</v>
       </c>
       <c r="J15" s="4">
-        <v>0.59150000000000003</v>
-      </c>
-      <c r="K15" s="4">
         <v>0.69</v>
       </c>
     </row>
-    <row r="16" spans="1:11">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A16" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C16" s="1">
         <v>2025</v>
       </c>
       <c r="D16" s="4">
-        <v>29</v>
+        <v>0.58140000000000003</v>
       </c>
       <c r="E16" s="4">
-        <v>0.58140000000000003</v>
+        <v>0.65339999999999998</v>
       </c>
       <c r="F16" s="4">
-        <v>0.65339999999999998</v>
+        <v>0.65380000000000005</v>
       </c>
       <c r="G16" s="4">
-        <v>0.65380000000000005</v>
+        <v>0.58560000000000001</v>
       </c>
       <c r="H16" s="4">
-        <v>0.58560000000000001</v>
+        <v>0.66520000000000001</v>
       </c>
       <c r="I16" s="4">
-        <v>0.66520000000000001</v>
+        <v>0.55700000000000005</v>
       </c>
       <c r="J16" s="4">
-        <v>0.55700000000000005</v>
-      </c>
-      <c r="K16" s="4">
         <v>0.62290000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:11">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A17" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C17" s="1">
         <v>12345</v>
       </c>
       <c r="D17" s="4">
-        <v>21</v>
+        <v>0.50180000000000002</v>
       </c>
       <c r="E17" s="4">
-        <v>0.50180000000000002</v>
+        <v>0.58079999999999998</v>
       </c>
       <c r="F17" s="4">
-        <v>0.58079999999999998</v>
+        <v>0.58130000000000004</v>
       </c>
       <c r="G17" s="4">
-        <v>0.58130000000000004</v>
+        <v>0.55030000000000001</v>
       </c>
       <c r="H17" s="4">
-        <v>0.55030000000000001</v>
+        <v>0.7853</v>
       </c>
       <c r="I17" s="4">
-        <v>0.7853</v>
+        <v>0.52890000000000004</v>
       </c>
       <c r="J17" s="4">
-        <v>0.52890000000000004</v>
-      </c>
-      <c r="K17" s="4">
         <v>0.64710000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:11">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A18" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18" s="1">
         <v>666</v>
       </c>
       <c r="D18" s="4">
-        <v>9</v>
+        <v>0.49690000000000001</v>
       </c>
       <c r="E18" s="4">
-        <v>0.49690000000000001</v>
+        <v>0.5373</v>
       </c>
       <c r="F18" s="4">
-        <v>0.5373</v>
+        <v>0.53790000000000004</v>
       </c>
       <c r="G18" s="4">
-        <v>0.53790000000000004</v>
+        <v>0.55500000000000005</v>
       </c>
       <c r="H18" s="4">
-        <v>0.55500000000000005</v>
+        <v>0.67059999999999997</v>
       </c>
       <c r="I18" s="4">
-        <v>0.67059999999999997</v>
+        <v>0.52310000000000001</v>
       </c>
       <c r="J18" s="4">
-        <v>0.52310000000000001</v>
-      </c>
-      <c r="K18" s="4">
         <v>0.60729999999999995</v>
       </c>
     </row>
-    <row r="19" spans="1:11">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A19" s="1"/>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
-      <c r="D19" s="1"/>
+      <c r="D19" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D14:D18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D14:D18),"0.0000")</f>
+        <v>0.5407±0.0389</v>
+      </c>
       <c r="E19" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
-        <v>0.5407±0.0389</v>
+        <f t="shared" ref="E19:J19" si="2" xml:space="preserve"> TEXT(AVERAGE(E14:E18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E14:E18),"0.0000")</f>
+        <v>0.6072±0.0476</v>
       </c>
       <c r="F19" t="str">
-        <f t="shared" ref="F19:K19" si="2" xml:space="preserve"> TEXT(AVERAGE(F14:F18),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F14:F18),"0.0000")</f>
-        <v>0.6072±0.0476</v>
+        <f t="shared" si="2"/>
+        <v>0.6076±0.0475</v>
       </c>
       <c r="G19" t="str">
         <f t="shared" si="2"/>
-        <v>0.6076±0.0475</v>
+        <v>0.5683±0.0191</v>
       </c>
       <c r="H19" t="str">
         <f t="shared" si="2"/>
-        <v>0.5683±0.0191</v>
+        <v>0.7201±0.0801</v>
       </c>
       <c r="I19" t="str">
         <f t="shared" si="2"/>
-        <v>0.7201±0.0801</v>
+        <v>0.5452±0.0293</v>
       </c>
       <c r="J19" t="str">
         <f t="shared" si="2"/>
-        <v>0.5452±0.0293</v>
-      </c>
-      <c r="K19" t="str">
-        <f t="shared" si="2"/>
         <v>0.6339±0.0359</v>
       </c>
     </row>
-    <row r="20" spans="1:11">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A20" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="1">
         <v>42</v>
       </c>
       <c r="D20" s="4">
-        <v>29</v>
+        <v>0.94630000000000003</v>
       </c>
       <c r="E20" s="4">
-        <v>0.94630000000000003</v>
+        <v>0.94199999999999995</v>
       </c>
       <c r="F20" s="4">
-        <v>0.94199999999999995</v>
+        <v>0.94210000000000005</v>
       </c>
       <c r="G20" s="4">
-        <v>0.94210000000000005</v>
+        <v>0.9052</v>
       </c>
       <c r="H20" s="4">
-        <v>0.9052</v>
+        <v>0.83409999999999995</v>
       </c>
       <c r="I20" s="4">
-        <v>0.83409999999999995</v>
+        <v>0.875</v>
       </c>
       <c r="J20" s="4">
-        <v>0.875</v>
-      </c>
-      <c r="K20" s="4">
         <v>0.86819999999999997</v>
       </c>
     </row>
-    <row r="21" spans="1:11">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A21" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C21" s="1">
         <v>1234</v>
       </c>
       <c r="D21" s="4">
-        <v>30</v>
+        <v>0.95279999999999998</v>
       </c>
       <c r="E21" s="4">
-        <v>0.95279999999999998</v>
+        <v>0.95030000000000003</v>
       </c>
       <c r="F21" s="4">
-        <v>0.95030000000000003</v>
+        <v>0.95040000000000002</v>
       </c>
       <c r="G21" s="4">
-        <v>0.95040000000000002</v>
+        <v>0.88239999999999996</v>
       </c>
       <c r="H21" s="4">
-        <v>0.88239999999999996</v>
+        <v>0.85150000000000003</v>
       </c>
       <c r="I21" s="4">
-        <v>0.85150000000000003</v>
+        <v>0.87070000000000003</v>
       </c>
       <c r="J21" s="4">
-        <v>0.87070000000000003</v>
-      </c>
-      <c r="K21" s="4">
         <v>0.86670000000000003</v>
       </c>
     </row>
-    <row r="22" spans="1:11">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A22" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C22" s="1">
         <v>2025</v>
       </c>
       <c r="D22" s="4">
-        <v>30</v>
+        <v>0.96109999999999995</v>
       </c>
       <c r="E22" s="4">
-        <v>0.96109999999999995</v>
+        <v>0.96150000000000002</v>
       </c>
       <c r="F22" s="4">
         <v>0.96150000000000002</v>
       </c>
       <c r="G22" s="4">
-        <v>0.96150000000000002</v>
+        <v>0.88739999999999997</v>
       </c>
       <c r="H22" s="4">
-        <v>0.88739999999999997</v>
+        <v>0.8952</v>
       </c>
       <c r="I22" s="4">
-        <v>0.8952</v>
+        <v>0.89219999999999999</v>
       </c>
       <c r="J22" s="4">
-        <v>0.89219999999999999</v>
-      </c>
-      <c r="K22" s="4">
         <v>0.89129999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:11">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A23" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C23" s="1">
         <v>12345</v>
       </c>
       <c r="D23" s="4">
-        <v>30</v>
+        <v>0.95650000000000002</v>
       </c>
       <c r="E23" s="4">
-        <v>0.95650000000000002</v>
+        <v>0.95779999999999998</v>
       </c>
       <c r="F23" s="4">
-        <v>0.95779999999999998</v>
+        <v>0.95789999999999997</v>
       </c>
       <c r="G23" s="4">
-        <v>0.95789999999999997</v>
+        <v>0.88790000000000002</v>
       </c>
       <c r="H23" s="4">
-        <v>0.88790000000000002</v>
+        <v>0.86460000000000004</v>
       </c>
       <c r="I23" s="4">
-        <v>0.86460000000000004</v>
+        <v>0.87929999999999997</v>
       </c>
       <c r="J23" s="4">
-        <v>0.87929999999999997</v>
-      </c>
-      <c r="K23" s="4">
         <v>0.87609999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:11">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A24" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" s="1">
         <v>666</v>
       </c>
       <c r="D24" s="4">
-        <v>29</v>
+        <v>0.94269999999999998</v>
       </c>
       <c r="E24" s="4">
-        <v>0.94269999999999998</v>
+        <v>0.93720000000000003</v>
       </c>
       <c r="F24" s="4">
-        <v>0.93720000000000003</v>
+        <v>0.93740000000000001</v>
       </c>
       <c r="G24" s="4">
-        <v>0.93740000000000001</v>
+        <v>0.85309999999999997</v>
       </c>
       <c r="H24" s="4">
-        <v>0.85309999999999997</v>
+        <v>0.91269999999999996</v>
       </c>
       <c r="I24" s="4">
-        <v>0.91269999999999996</v>
+        <v>0.87929999999999997</v>
       </c>
       <c r="J24" s="4">
-        <v>0.87929999999999997</v>
-      </c>
-      <c r="K24" s="4">
         <v>0.88190000000000002</v>
       </c>
     </row>
-    <row r="25" spans="1:11">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A25" s="1"/>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
-      <c r="D25" s="1"/>
+      <c r="D25" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D20:D24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D20:D24),"0.0000")</f>
+        <v>0.9519±0.0075</v>
+      </c>
       <c r="E25" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
-        <v>0.9519±0.0075</v>
+        <f t="shared" ref="E25:J25" si="3" xml:space="preserve"> TEXT(AVERAGE(E20:E24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E20:E24),"0.0000")</f>
+        <v>0.9498±0.0103</v>
       </c>
       <c r="F25" t="str">
-        <f t="shared" ref="F25:K25" si="3" xml:space="preserve"> TEXT(AVERAGE(F20:F24),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F20:F24),"0.0000")</f>
-        <v>0.9498±0.0103</v>
+        <f t="shared" si="3"/>
+        <v>0.9499±0.0102</v>
       </c>
       <c r="G25" t="str">
         <f t="shared" si="3"/>
-        <v>0.9499±0.0102</v>
+        <v>0.8832±0.0189</v>
       </c>
       <c r="H25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8832±0.0189</v>
+        <v>0.8716±0.0320</v>
       </c>
       <c r="I25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8716±0.0320</v>
+        <v>0.8793±0.0080</v>
       </c>
       <c r="J25" t="str">
         <f t="shared" si="3"/>
-        <v>0.8793±0.0080</v>
-      </c>
-      <c r="K25" t="str">
-        <f t="shared" si="3"/>
         <v>0.8768±0.0102</v>
       </c>
     </row>
-    <row r="26" spans="1:11">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A26" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>42</v>
       </c>
       <c r="D26" s="4">
-        <v>7</v>
+        <v>0.65359999999999996</v>
       </c>
       <c r="E26" s="4">
-        <v>0.65359999999999996</v>
+        <v>0.70750000000000002</v>
       </c>
       <c r="F26" s="4">
-        <v>0.70750000000000002</v>
+        <v>0.71130000000000004</v>
       </c>
       <c r="G26" s="4">
-        <v>0.71130000000000004</v>
+        <v>0.69110000000000005</v>
       </c>
       <c r="H26" s="4">
-        <v>0.69110000000000005</v>
+        <v>0.88539999999999996</v>
       </c>
       <c r="I26" s="4">
-        <v>0.88539999999999996</v>
+        <v>0.69369999999999998</v>
       </c>
       <c r="J26" s="4">
-        <v>0.69369999999999998</v>
-      </c>
-      <c r="K26" s="4">
         <v>0.77629999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:11">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A27" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C27" s="1">
         <v>1234</v>
       </c>
       <c r="D27" s="4">
-        <v>17</v>
+        <v>0.59650000000000003</v>
       </c>
       <c r="E27" s="4">
-        <v>0.59650000000000003</v>
+        <v>0.70760000000000001</v>
       </c>
       <c r="F27" s="4">
-        <v>0.70760000000000001</v>
+        <v>0.71099999999999997</v>
       </c>
       <c r="G27" s="4">
-        <v>0.71099999999999997</v>
+        <v>0.61219999999999997</v>
       </c>
       <c r="H27" s="4">
-        <v>0.61219999999999997</v>
+        <v>0.9375</v>
       </c>
       <c r="I27" s="4">
-        <v>0.9375</v>
+        <v>0.60619999999999996</v>
       </c>
       <c r="J27" s="4">
-        <v>0.60619999999999996</v>
-      </c>
-      <c r="K27" s="4">
         <v>0.74070000000000003</v>
       </c>
     </row>
-    <row r="28" spans="1:11">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A28" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C28" s="1">
         <v>2025</v>
       </c>
       <c r="D28" s="4">
-        <v>10</v>
+        <v>0.60089999999999999</v>
       </c>
       <c r="E28" s="4">
-        <v>0.60089999999999999</v>
+        <v>0.67789999999999995</v>
       </c>
       <c r="F28" s="4">
-        <v>0.67789999999999995</v>
+        <v>0.68510000000000004</v>
       </c>
       <c r="G28" s="4">
-        <v>0.68510000000000004</v>
+        <v>0.68030000000000002</v>
       </c>
       <c r="H28" s="4">
-        <v>0.68030000000000002</v>
+        <v>0.86460000000000004</v>
       </c>
       <c r="I28" s="4">
-        <v>0.86460000000000004</v>
+        <v>0.67500000000000004</v>
       </c>
       <c r="J28" s="4">
-        <v>0.67500000000000004</v>
-      </c>
-      <c r="K28" s="4">
         <v>0.76149999999999995</v>
       </c>
     </row>
-    <row r="29" spans="1:11">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A29" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C29" s="1">
         <v>12345</v>
       </c>
       <c r="D29" s="4">
-        <v>6</v>
+        <v>0.5988</v>
       </c>
       <c r="E29" s="4">
-        <v>0.5988</v>
+        <v>0.68759999999999999</v>
       </c>
       <c r="F29" s="4">
-        <v>0.68759999999999999</v>
+        <v>0.69099999999999995</v>
       </c>
       <c r="G29" s="4">
-        <v>0.69099999999999995</v>
+        <v>0.61609999999999998</v>
       </c>
       <c r="H29" s="4">
-        <v>0.61609999999999998</v>
+        <v>0.71879999999999999</v>
       </c>
       <c r="I29" s="4">
-        <v>0.71879999999999999</v>
+        <v>0.5625</v>
       </c>
       <c r="J29" s="4">
-        <v>0.5625</v>
-      </c>
-      <c r="K29" s="4">
         <v>0.66349999999999998</v>
       </c>
     </row>
-    <row r="30" spans="1:11">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.4">
       <c r="A30" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C30" s="1">
         <v>666</v>
       </c>
       <c r="D30" s="4">
-        <v>26</v>
+        <v>0.69910000000000005</v>
       </c>
       <c r="E30" s="4">
-        <v>0.69910000000000005</v>
+        <v>0.78910000000000002</v>
       </c>
       <c r="F30" s="4">
-        <v>0.78910000000000002</v>
+        <v>0.79139999999999999</v>
       </c>
       <c r="G30" s="4">
-        <v>0.79139999999999999</v>
+        <v>0.69230000000000003</v>
       </c>
       <c r="H30" s="4">
-        <v>0.69230000000000003</v>
+        <v>0.75</v>
       </c>
       <c r="I30" s="4">
-        <v>0.75</v>
+        <v>0.65</v>
       </c>
       <c r="J30" s="4">
-        <v>0.65</v>
-      </c>
-      <c r="K30" s="4">
         <v>0.72</v>
       </c>
     </row>
-    <row r="31" spans="1:11">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="D31" t="str">
+        <f xml:space="preserve"> TEXT(AVERAGE(D26:D30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(D26:D30),"0.0000")</f>
+        <v>0.6298±0.0455</v>
+      </c>
       <c r="E31" t="str">
-        <f xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
-        <v>0.6298±0.0455</v>
+        <f t="shared" ref="E31:J31" si="4" xml:space="preserve"> TEXT(AVERAGE(E26:E30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(E26:E30),"0.0000")</f>
+        <v>0.7139±0.0439</v>
       </c>
       <c r="F31" t="str">
-        <f t="shared" ref="F31:K31" si="4" xml:space="preserve"> TEXT(AVERAGE(F26:F30),"0.0000") &amp; "±" &amp; TEXT(_xlfn.STDEV.S(F26:F30),"0.0000")</f>
-        <v>0.7139±0.0439</v>
+        <f t="shared" si="4"/>
+        <v>0.7180±0.0427</v>
       </c>
       <c r="G31" t="str">
         <f t="shared" si="4"/>
-        <v>0.7180±0.0427</v>
+        <v>0.6584±0.0407</v>
       </c>
       <c r="H31" t="str">
         <f t="shared" si="4"/>
-        <v>0.6584±0.0407</v>
+        <v>0.8313±0.0930</v>
       </c>
       <c r="I31" t="str">
         <f t="shared" si="4"/>
-        <v>0.8313±0.0930</v>
+        <v>0.6375±0.0532</v>
       </c>
       <c r="J31" t="str">
-        <f t="shared" si="4"/>
-        <v>0.6375±0.0532</v>
-      </c>
-      <c r="K31" t="str">
         <f t="shared" si="4"/>
         <v>0.7324±0.0440</v>
       </c>
